--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/catherine115817/Documents/purdue/james/run7/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F8CF5E-6337-CD4F-9A2C-0016291B1A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="5700" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t>Solution Label</t>
   </si>
@@ -631,24 +625,6 @@
     <t>PM 404</t>
   </si>
   <si>
-    <t>PM 356</t>
-  </si>
-  <si>
-    <t>PM 357</t>
-  </si>
-  <si>
-    <t>PM 358</t>
-  </si>
-  <si>
-    <t>PM 359</t>
-  </si>
-  <si>
-    <t>PM 360</t>
-  </si>
-  <si>
-    <t>PM 361</t>
-  </si>
-  <si>
     <t>PM 499</t>
   </si>
   <si>
@@ -691,62 +667,248 @@
     <t>PM 505</t>
   </si>
   <si>
-    <t>PM 618</t>
-  </si>
-  <si>
-    <t>PM 619</t>
-  </si>
-  <si>
-    <t>PM 621</t>
-  </si>
-  <si>
-    <t>PM 623</t>
-  </si>
-  <si>
-    <t>PM 624</t>
-  </si>
-  <si>
-    <t>PM 625</t>
-  </si>
-  <si>
-    <t>PM 626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM 631 </t>
-  </si>
-  <si>
-    <t>PM 632</t>
-  </si>
-  <si>
-    <t>PM 633</t>
-  </si>
-  <si>
-    <t>PM 634</t>
-  </si>
-  <si>
-    <t>PM 635</t>
-  </si>
-  <si>
-    <t>PM 636</t>
+    <t>PM 535</t>
+  </si>
+  <si>
+    <t>PM 536</t>
+  </si>
+  <si>
+    <t>PM 537</t>
+  </si>
+  <si>
+    <t>PM 538</t>
+  </si>
+  <si>
+    <t>PM 539</t>
+  </si>
+  <si>
+    <t>PM 540-2</t>
+  </si>
+  <si>
+    <t>PM 541-2</t>
+  </si>
+  <si>
+    <t>PM 542</t>
+  </si>
+  <si>
+    <t>PM 543</t>
+  </si>
+  <si>
+    <t>PM 544</t>
+  </si>
+  <si>
+    <t>PM 545</t>
+  </si>
+  <si>
+    <t>PM 546</t>
+  </si>
+  <si>
+    <t>PM 547-2</t>
+  </si>
+  <si>
+    <t>PM 548-2</t>
+  </si>
+  <si>
+    <t>PM 602</t>
+  </si>
+  <si>
+    <t>PM 603</t>
+  </si>
+  <si>
+    <t>PM 604</t>
+  </si>
+  <si>
+    <t>PM 605</t>
+  </si>
+  <si>
+    <t>PM 606</t>
+  </si>
+  <si>
+    <t>PM 607</t>
+  </si>
+  <si>
+    <t>PM 608</t>
+  </si>
+  <si>
+    <t>PM 609</t>
+  </si>
+  <si>
+    <t>PM 610</t>
+  </si>
+  <si>
+    <t>PM 611</t>
+  </si>
+  <si>
+    <t>PM 612</t>
+  </si>
+  <si>
+    <t>PM 613</t>
+  </si>
+  <si>
+    <t>PM 614</t>
+  </si>
+  <si>
+    <t>PM 615</t>
+  </si>
+  <si>
+    <t>PM 549</t>
+  </si>
+  <si>
+    <t>PM 550</t>
+  </si>
+  <si>
+    <t>PM 551</t>
+  </si>
+  <si>
+    <t>PM 552</t>
+  </si>
+  <si>
+    <t>PM 553-2</t>
+  </si>
+  <si>
+    <t>PM 554-2</t>
+  </si>
+  <si>
+    <t>PM 555-2</t>
+  </si>
+  <si>
+    <t>PM 556</t>
+  </si>
+  <si>
+    <t>PM 557</t>
+  </si>
+  <si>
+    <t>PM 558</t>
+  </si>
+  <si>
+    <t>PM 559</t>
+  </si>
+  <si>
+    <t>PM 560-2</t>
+  </si>
+  <si>
+    <t>PM 561-2</t>
+  </si>
+  <si>
+    <t>PM 562-2</t>
+  </si>
+  <si>
+    <t>PM 577</t>
+  </si>
+  <si>
+    <t>PM 582</t>
+  </si>
+  <si>
+    <t>PM 583</t>
+  </si>
+  <si>
+    <t>PM 598</t>
+  </si>
+  <si>
+    <t>PM 599</t>
+  </si>
+  <si>
+    <t>PM 600</t>
+  </si>
+  <si>
+    <t>PM 601</t>
+  </si>
+  <si>
+    <t>PM 584</t>
+  </si>
+  <si>
+    <t>PM 585</t>
+  </si>
+  <si>
+    <t>PM 586</t>
+  </si>
+  <si>
+    <t>PM 587</t>
+  </si>
+  <si>
+    <t>PM 588</t>
+  </si>
+  <si>
+    <t>PM 589</t>
+  </si>
+  <si>
+    <t>PM 590</t>
+  </si>
+  <si>
+    <t>PM 591</t>
+  </si>
+  <si>
+    <t>PM 592</t>
+  </si>
+  <si>
+    <t>PM 593</t>
+  </si>
+  <si>
+    <t>PM 594</t>
+  </si>
+  <si>
+    <t>PM 595</t>
+  </si>
+  <si>
+    <t>PM 596</t>
+  </si>
+  <si>
+    <t>PM 597</t>
+  </si>
+  <si>
+    <t>PM 563</t>
+  </si>
+  <si>
+    <t>PM 564</t>
+  </si>
+  <si>
+    <t>PM 565</t>
+  </si>
+  <si>
+    <t>PM 566-3</t>
+  </si>
+  <si>
+    <t>PM 567-2</t>
+  </si>
+  <si>
+    <t>PM 568-2</t>
+  </si>
+  <si>
+    <t>PM 569-2</t>
+  </si>
+  <si>
+    <t>PM 570</t>
+  </si>
+  <si>
+    <t>PM 571</t>
+  </si>
+  <si>
+    <t>PM 572</t>
+  </si>
+  <si>
+    <t>PM 573-2</t>
+  </si>
+  <si>
+    <t>PM 574-2</t>
+  </si>
+  <si>
+    <t>PM 575-2</t>
+  </si>
+  <si>
+    <t>PM 576-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -757,7 +919,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -765,44 +927,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1090,45 +1226,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I231"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="30.5" customWidth="1"/>
-    <col min="9" max="9" width="19.1640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I286"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1148,16 +1279,16 @@
         <v>40000</v>
       </c>
       <c r="G2">
-        <v>53.132220741586828</v>
+        <v>53.13222074158683</v>
       </c>
       <c r="H2">
-        <v>0.17848800000000001</v>
+        <v>0.178488</v>
       </c>
       <c r="I2">
-        <v>3.0346061531167348E-9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.034606153116735E-09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1177,16 +1308,16 @@
         <v>40000</v>
       </c>
       <c r="G3">
-        <v>52.736721488972528</v>
+        <v>52.73672148897253</v>
       </c>
       <c r="H3">
         <v>0.203352</v>
       </c>
       <c r="I3">
-        <v>3.4573931540020929E-9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.457393154002093E-09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1206,16 +1337,16 @@
         <v>40000</v>
       </c>
       <c r="G4">
-        <v>53.248296527984962</v>
+        <v>53.24829652798496</v>
       </c>
       <c r="H4">
-        <v>0.17893200000000001</v>
+        <v>0.178932</v>
       </c>
       <c r="I4">
-        <v>3.0421405159200609E-9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.042140515920061E-09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1235,16 +1366,16 @@
         <v>40000</v>
       </c>
       <c r="G5">
-        <v>51.938954345902239</v>
+        <v>51.93895434590224</v>
       </c>
       <c r="H5">
         <v>0.21756</v>
       </c>
       <c r="I5">
-        <v>3.6990781563543438E-9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.699078156354344E-09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1264,16 +1395,16 @@
         <v>40000</v>
       </c>
       <c r="G6">
-        <v>51.485374339706162</v>
+        <v>51.48537433970616</v>
       </c>
       <c r="H6">
-        <v>0.16783200000000001</v>
+        <v>0.167832</v>
       </c>
       <c r="I6">
-        <v>2.8536273951406429E-9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.853627395140643E-09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1293,16 +1424,16 @@
         <v>40000</v>
       </c>
       <c r="G7">
-        <v>51.020217770282343</v>
+        <v>51.02021777028234</v>
       </c>
       <c r="H7">
-        <v>0.17804400000000001</v>
+        <v>0.178044</v>
       </c>
       <c r="I7">
-        <v>3.0273182714274389E-9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.027318271427439E-09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1322,16 +1453,16 @@
         <v>40000</v>
       </c>
       <c r="G8">
-        <v>51.025843298552559</v>
+        <v>51.02584329855256</v>
       </c>
       <c r="H8">
-        <v>0.17715600000000001</v>
+        <v>0.177156</v>
       </c>
       <c r="I8">
-        <v>3.0122187356815331E-9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.012218735681533E-09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1351,16 +1482,16 @@
         <v>100000</v>
       </c>
       <c r="G9">
-        <v>79.213089121222055</v>
+        <v>79.21308912122205</v>
       </c>
       <c r="H9">
-        <v>0.86358000000000001</v>
+        <v>0.86358</v>
       </c>
       <c r="I9">
-        <v>1.466675213858826E-8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.466675213858826E-08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1383,13 +1514,13 @@
         <v>50.96835522357479</v>
       </c>
       <c r="H10">
-        <v>0.29037600000000002</v>
+        <v>0.290376</v>
       </c>
       <c r="I10">
-        <v>4.9373325179363676E-9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.937332517936368E-09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1409,16 +1540,16 @@
         <v>100000</v>
       </c>
       <c r="G11">
-        <v>52.642902628920517</v>
+        <v>52.64290262892052</v>
       </c>
       <c r="H11">
-        <v>0.18603600000000001</v>
+        <v>0.186036</v>
       </c>
       <c r="I11">
-        <v>3.162998422165814E-9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.162998422165814E-09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1438,16 +1569,16 @@
         <v>100000</v>
       </c>
       <c r="G12">
-        <v>53.191818695614543</v>
+        <v>53.19181869561454</v>
       </c>
       <c r="H12">
         <v>0.222444</v>
       </c>
       <c r="I12">
-        <v>3.7819253370516767E-9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.781925337051677E-09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1467,16 +1598,16 @@
         <v>100000</v>
       </c>
       <c r="G13">
-        <v>52.451423448014353</v>
+        <v>52.45142344801435</v>
       </c>
       <c r="H13">
         <v>0.20868</v>
       </c>
       <c r="I13">
-        <v>3.5480211786167809E-9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.548021178616781E-09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1496,16 +1627,16 @@
         <v>100000</v>
       </c>
       <c r="G14">
-        <v>52.238615879696333</v>
+        <v>52.23861587969633</v>
       </c>
       <c r="H14">
         <v>0.20868</v>
       </c>
       <c r="I14">
-        <v>3.548051988756034E-9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.548051988756034E-09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1525,16 +1656,16 @@
         <v>100000</v>
       </c>
       <c r="G15">
-        <v>71.046771419376839</v>
+        <v>71.04677141937684</v>
       </c>
       <c r="H15">
-        <v>7.3237800000000011</v>
+        <v>7.323780000000001</v>
       </c>
       <c r="I15">
-        <v>1.2442603232398811E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.244260323239881E-07</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1554,16 +1685,16 @@
         <v>100000</v>
       </c>
       <c r="G16">
-        <v>78.415542189424627</v>
+        <v>78.41554218942463</v>
       </c>
       <c r="H16">
-        <v>8.1389640000000014</v>
+        <v>8.138964000000001</v>
       </c>
       <c r="I16">
-        <v>1.3823391973698499E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.38233919736985E-07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1583,21 +1714,21 @@
         <v>100000</v>
       </c>
       <c r="G17">
-        <v>78.192701499121995</v>
+        <v>78.19270149912199</v>
       </c>
       <c r="H17">
         <v>10.09212</v>
       </c>
       <c r="I17">
-        <v>1.7140829941765201E-7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.71408299417652E-07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1612,21 +1743,21 @@
         <v>100000</v>
       </c>
       <c r="G18">
-        <v>51.986597937713583</v>
+        <v>51.98659793771358</v>
       </c>
       <c r="H18">
-        <v>0.18070800000000001</v>
+        <v>0.180708</v>
       </c>
       <c r="I18">
-        <v>3.0724936381081408E-9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.072493638108141E-09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -1641,21 +1772,21 @@
         <v>100000</v>
       </c>
       <c r="G19">
-        <v>52.436299945530052</v>
+        <v>52.43629994553005</v>
       </c>
       <c r="H19">
-        <v>0.17493600000000001</v>
+        <v>0.174936</v>
       </c>
       <c r="I19">
-        <v>2.974300440550874E-9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.974300440550874E-09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C20">
         <v>25</v>
@@ -1670,21 +1801,21 @@
         <v>100000</v>
       </c>
       <c r="G20">
-        <v>56.603079559332407</v>
+        <v>56.60307955933241</v>
       </c>
       <c r="H20">
-        <v>0.20202000000000001</v>
+        <v>0.20202</v>
       </c>
       <c r="I20">
-        <v>3.4342046729462961E-9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.434204672946296E-09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C21">
         <v>50</v>
@@ -1699,21 +1830,21 @@
         <v>100000</v>
       </c>
       <c r="G21">
-        <v>78.447689066426264</v>
+        <v>78.44768906642626</v>
       </c>
       <c r="H21">
         <v>13.074024</v>
       </c>
       <c r="I21">
-        <v>2.2205175204765559E-7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.220517520476556E-07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1728,21 +1859,21 @@
         <v>100000</v>
       </c>
       <c r="G22">
-        <v>75.527963519632365</v>
+        <v>75.52796351963237</v>
       </c>
       <c r="H22">
-        <v>23.365943999999999</v>
+        <v>23.365944</v>
       </c>
       <c r="I22">
-        <v>3.9689894826571102E-7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.96898948265711E-07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C23">
         <v>250</v>
@@ -1757,21 +1888,21 @@
         <v>100000</v>
       </c>
       <c r="G23">
-        <v>67.345710555607923</v>
+        <v>67.34571055560792</v>
       </c>
       <c r="H23">
-        <v>24.104316000000001</v>
+        <v>24.104316</v>
       </c>
       <c r="I23">
-        <v>4.0957771468162992E-7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.095777146816299E-07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C24">
         <v>500</v>
@@ -1786,21 +1917,21 @@
         <v>100000</v>
       </c>
       <c r="G24">
-        <v>57.486978640684526</v>
+        <v>57.48697864068453</v>
       </c>
       <c r="H24">
-        <v>22.780308000000002</v>
+        <v>22.780308</v>
       </c>
       <c r="I24">
-        <v>3.8723601179054527E-7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.872360117905453E-07</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>32</v>
       </c>
       <c r="B25">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C25">
         <v>1000</v>
@@ -1815,16 +1946,16 @@
         <v>100000</v>
       </c>
       <c r="G25">
-        <v>60.049218923143052</v>
+        <v>60.04921892314305</v>
       </c>
       <c r="H25">
-        <v>26.444196000000009</v>
+        <v>26.44419600000001</v>
       </c>
       <c r="I25">
-        <v>4.4947042366861738E-7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.494704236686174E-07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1844,16 +1975,16 @@
         <v>100000</v>
       </c>
       <c r="G26">
-        <v>43.464049537396257</v>
+        <v>43.46404953739626</v>
       </c>
       <c r="H26">
-        <v>4.4844000000000009E-2</v>
+        <v>0.04484400000000001</v>
       </c>
       <c r="I26">
-        <v>7.6272682107338359E-10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.627268210733836E-10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1873,16 +2004,16 @@
         <v>100000</v>
       </c>
       <c r="G27">
-        <v>65.492245038658794</v>
+        <v>65.49224503865879</v>
       </c>
       <c r="H27">
-        <v>6.8376000000000006E-2</v>
+        <v>0.06837600000000001</v>
       </c>
       <c r="I27">
-        <v>1.1619248090926459E-9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.161924809092646E-09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1902,16 +2033,16 @@
         <v>100000</v>
       </c>
       <c r="G28">
-        <v>74.494123394307877</v>
+        <v>74.49412339430788</v>
       </c>
       <c r="H28">
-        <v>21.038495999999999</v>
+        <v>21.038496</v>
       </c>
       <c r="I28">
-        <v>3.5737947844066582E-7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.573794784406658E-07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1931,16 +2062,16 @@
         <v>100000</v>
       </c>
       <c r="G29">
-        <v>64.781883158447656</v>
+        <v>64.78188315844766</v>
       </c>
       <c r="H29">
-        <v>29.199660000000002</v>
+        <v>29.19966</v>
       </c>
       <c r="I29">
-        <v>4.962090839774931E-7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.962090839774931E-07</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1960,16 +2091,16 @@
         <v>100000</v>
       </c>
       <c r="G30">
-        <v>55.018869816996407</v>
+        <v>55.01886981699641</v>
       </c>
       <c r="H30">
-        <v>30.638663999999999</v>
+        <v>30.638664</v>
       </c>
       <c r="I30">
-        <v>5.2087042961899902E-7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.20870429618999E-07</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1989,16 +2120,16 @@
         <v>100000</v>
       </c>
       <c r="G31">
-        <v>62.272572935164582</v>
+        <v>62.27257293516458</v>
       </c>
       <c r="H31">
-        <v>36.522551999999997</v>
+        <v>36.522552</v>
       </c>
       <c r="I31">
-        <v>6.2071534333658602E-7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.20715343336586E-07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2018,16 +2149,16 @@
         <v>100000</v>
       </c>
       <c r="G32">
-        <v>54.334271399546779</v>
+        <v>54.33427139954678</v>
       </c>
       <c r="H32">
-        <v>33.849227999999997</v>
+        <v>33.849228</v>
       </c>
       <c r="I32">
-        <v>5.7546746884441771E-7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.754674688444177E-07</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2047,16 +2178,16 @@
         <v>100000</v>
       </c>
       <c r="G33">
-        <v>53.390092638166827</v>
+        <v>53.39009263816683</v>
       </c>
       <c r="H33">
-        <v>33.564180000000007</v>
+        <v>33.56418000000001</v>
       </c>
       <c r="I33">
-        <v>5.7064337899330834E-7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.706433789933083E-07</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2079,13 +2210,13 @@
         <v>60.6869936190581</v>
       </c>
       <c r="H34">
-        <v>6.7932000000000006E-2</v>
+        <v>0.06793200000000001</v>
       </c>
       <c r="I34">
-        <v>1.1546061172640961E-9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.154606117264096E-09</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2105,16 +2236,16 @@
         <v>100000</v>
       </c>
       <c r="G35">
-        <v>68.420997058427758</v>
+        <v>68.42099705842776</v>
       </c>
       <c r="H35">
-        <v>6.2897040000000004</v>
+        <v>6.289704</v>
       </c>
       <c r="I35">
-        <v>1.068692275031265E-7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.068692275031265E-07</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2134,16 +2265,16 @@
         <v>100000</v>
       </c>
       <c r="G36">
-        <v>61.399511272534568</v>
+        <v>61.39951127253457</v>
       </c>
       <c r="H36">
         <v>31.669632</v>
       </c>
       <c r="I36">
-        <v>5.3825719970009841E-7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.382571997000984E-07</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2163,16 +2294,16 @@
         <v>100000</v>
       </c>
       <c r="G37">
-        <v>54.597200425130289</v>
+        <v>54.59720042513029</v>
       </c>
       <c r="H37">
-        <v>38.518776000000003</v>
+        <v>38.518776</v>
       </c>
       <c r="I37">
-        <v>6.5484697992255093E-7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.548469799225509E-07</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2192,16 +2323,16 @@
         <v>100000</v>
       </c>
       <c r="G38">
-        <v>52.395728880962928</v>
+        <v>52.39572888096293</v>
       </c>
       <c r="H38">
-        <v>35.190996000000013</v>
+        <v>35.19099600000001</v>
       </c>
       <c r="I38">
-        <v>5.9832606317171491E-7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.983260631717149E-07</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2221,16 +2352,16 @@
         <v>100000</v>
       </c>
       <c r="G39">
-        <v>52.201673555251261</v>
+        <v>52.20167355525126</v>
       </c>
       <c r="H39">
-        <v>32.835132000000002</v>
+        <v>32.835132</v>
       </c>
       <c r="I39">
-        <v>5.5827549843626122E-7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.582754984362612E-07</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2250,16 +2381,16 @@
         <v>100000</v>
       </c>
       <c r="G40">
-        <v>52.161173064107963</v>
+        <v>52.16117306410796</v>
       </c>
       <c r="H40">
         <v>30.48948</v>
       </c>
       <c r="I40">
-        <v>5.1839468087926992E-7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.183946808792699E-07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2279,16 +2410,16 @@
         <v>100000</v>
       </c>
       <c r="G41">
-        <v>52.255359097408828</v>
+        <v>52.25535909740883</v>
       </c>
       <c r="H41">
-        <v>30.665303999999999</v>
+        <v>30.665304</v>
       </c>
       <c r="I41">
-        <v>5.213821090066544E-7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.213821090066544E-07</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2308,16 +2439,16 @@
         <v>100000</v>
       </c>
       <c r="G42">
-        <v>58.339667139638728</v>
+        <v>58.33966713963873</v>
       </c>
       <c r="H42">
         <v>0.210456</v>
       </c>
       <c r="I42">
-        <v>3.577357566209489E-9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.577357566209489E-09</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2337,16 +2468,16 @@
         <v>100000</v>
       </c>
       <c r="G43">
-        <v>65.432668657902482</v>
+        <v>65.43266865790248</v>
       </c>
       <c r="H43">
-        <v>16.760556000000001</v>
+        <v>16.760556</v>
       </c>
       <c r="I43">
-        <v>2.8481562461499969E-7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.848156246149997E-07</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2369,13 +2500,13 @@
         <v>51.24549883106436</v>
       </c>
       <c r="H44">
-        <v>19.704719999999998</v>
+        <v>19.70472</v>
       </c>
       <c r="I44">
-        <v>3.3504027373837238E-7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.350402737383724E-07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2395,16 +2526,16 @@
         <v>50000</v>
       </c>
       <c r="G45">
-        <v>50.740527836498082</v>
+        <v>50.74052783649808</v>
       </c>
       <c r="H45">
-        <v>20.447088000000001</v>
+        <v>20.447088</v>
       </c>
       <c r="I45">
-        <v>3.476699557511928E-7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.476699557511928E-07</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2424,16 +2555,16 @@
         <v>50000</v>
       </c>
       <c r="G46">
-        <v>50.380461277103002</v>
+        <v>50.380461277103</v>
       </c>
       <c r="H46">
-        <v>19.371276000000002</v>
+        <v>19.371276</v>
       </c>
       <c r="I46">
-        <v>3.293823369947456E-7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.293823369947456E-07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2453,16 +2584,16 @@
         <v>50000</v>
       </c>
       <c r="G47">
-        <v>50.546127044756993</v>
+        <v>50.54612704475699</v>
       </c>
       <c r="H47">
-        <v>20.414231999999998</v>
+        <v>20.414232</v>
       </c>
       <c r="I47">
-        <v>3.4711404584112711E-7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.471140458411271E-07</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2482,16 +2613,16 @@
         <v>50000</v>
       </c>
       <c r="G48">
-        <v>51.749693932390457</v>
+        <v>51.74969393239046</v>
       </c>
       <c r="H48">
-        <v>18.500147999999999</v>
+        <v>18.500148</v>
       </c>
       <c r="I48">
-        <v>3.1455240793989091E-7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.145524079398909E-07</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2511,16 +2642,16 @@
         <v>50000</v>
       </c>
       <c r="G49">
-        <v>52.069781058917172</v>
+        <v>52.06978105891717</v>
       </c>
       <c r="H49">
-        <v>19.372164000000009</v>
+        <v>19.37216400000001</v>
       </c>
       <c r="I49">
-        <v>3.2937472945786159E-7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.293747294578616E-07</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2540,16 +2671,16 @@
         <v>50000</v>
       </c>
       <c r="G50">
-        <v>58.161597545877967</v>
+        <v>58.16159754587797</v>
       </c>
       <c r="H50">
-        <v>0.61272000000000004</v>
+        <v>0.61272</v>
       </c>
       <c r="I50">
-        <v>1.0415167308799971E-8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.041516730879997E-08</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2569,16 +2700,16 @@
         <v>50000</v>
       </c>
       <c r="G51">
-        <v>60.967225725141631</v>
+        <v>60.96722572514163</v>
       </c>
       <c r="H51">
         <v>13.541556</v>
       </c>
       <c r="I51">
-        <v>2.3015640154227651E-7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.301564015422765E-07</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2598,16 +2729,16 @@
         <v>50000</v>
       </c>
       <c r="G52">
-        <v>50.723414677251327</v>
+        <v>50.72341467725133</v>
       </c>
       <c r="H52">
-        <v>20.790299999999998</v>
+        <v>20.7903</v>
       </c>
       <c r="I52">
-        <v>3.5350597253219418E-7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.535059725321942E-07</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -2627,16 +2758,16 @@
         <v>50000</v>
       </c>
       <c r="G53">
-        <v>50.550965216193539</v>
+        <v>50.55096521619354</v>
       </c>
       <c r="H53">
         <v>22.438872</v>
       </c>
       <c r="I53">
-        <v>3.815400014173358E-7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.815400014173358E-07</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2659,13 +2790,13 @@
         <v>50.67595133595826</v>
       </c>
       <c r="H54">
-        <v>23.884979999999999</v>
+        <v>23.88498</v>
       </c>
       <c r="I54">
-        <v>4.0612686868221909E-7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.061268686822191E-07</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2685,16 +2816,16 @@
         <v>50000</v>
       </c>
       <c r="G55">
-        <v>50.426497555380863</v>
+        <v>50.42649755538086</v>
       </c>
       <c r="H55">
-        <v>22.346520000000002</v>
+        <v>22.34652</v>
       </c>
       <c r="I55">
-        <v>3.7997162154867378E-7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.799716215486738E-07</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2714,16 +2845,16 @@
         <v>50000</v>
       </c>
       <c r="G56">
-        <v>50.400963782247793</v>
+        <v>50.40096378224779</v>
       </c>
       <c r="H56">
-        <v>20.567855999999999</v>
+        <v>20.567856</v>
       </c>
       <c r="I56">
-        <v>3.4972826818422031E-7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.497282681842203E-07</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2743,16 +2874,16 @@
         <v>50000</v>
       </c>
       <c r="G57">
-        <v>50.496268330987903</v>
+        <v>50.4962683309879</v>
       </c>
       <c r="H57">
-        <v>20.853791999999999</v>
+        <v>20.853792</v>
       </c>
       <c r="I57">
-        <v>3.5458883980771773E-7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.545888398077177E-07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2772,16 +2903,16 @@
         <v>100000</v>
       </c>
       <c r="G58">
-        <v>45.119516683083909</v>
+        <v>45.11951668308391</v>
       </c>
       <c r="H58">
         <v>0.120768</v>
       </c>
       <c r="I58">
-        <v>2.0539373932534649E-9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.053937393253465E-09</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -2804,18 +2935,18 @@
         <v>25.45440088476704</v>
       </c>
       <c r="H59">
-        <v>4.1736000000000002E-2</v>
+        <v>0.041736</v>
       </c>
       <c r="I59">
-        <v>7.1038681326039951E-10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.103868132603995E-10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>67</v>
       </c>
       <c r="B60">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C60">
         <v>1000</v>
@@ -2830,21 +2961,21 @@
         <v>100000</v>
       </c>
       <c r="G60">
-        <v>87.535395627343519</v>
+        <v>87.53539562734352</v>
       </c>
       <c r="H60">
-        <v>2.9885640000000002</v>
+        <v>2.988564</v>
       </c>
       <c r="I60">
-        <v>5.073955330560325E-8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.073955330560325E-08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>68</v>
       </c>
       <c r="B61">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C61">
         <v>250</v>
@@ -2859,21 +2990,21 @@
         <v>100000</v>
       </c>
       <c r="G61">
-        <v>78.040527252074469</v>
+        <v>78.04052725207447</v>
       </c>
       <c r="H61">
-        <v>0.47463600000000011</v>
+        <v>0.4746360000000001</v>
       </c>
       <c r="I61">
-        <v>8.0614434093408337E-9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.061443409340834E-09</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>69</v>
       </c>
       <c r="B62">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C62">
         <v>500</v>
@@ -2888,16 +3019,16 @@
         <v>100000</v>
       </c>
       <c r="G62">
-        <v>85.934457280811074</v>
+        <v>85.93445728081107</v>
       </c>
       <c r="H62">
         <v>1.035852</v>
       </c>
       <c r="I62">
-        <v>1.7587743335695472E-8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.758774333569547E-08</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -2917,21 +3048,21 @@
         <v>100000</v>
       </c>
       <c r="G63">
-        <v>35.448730679693938</v>
+        <v>35.44873067969394</v>
       </c>
       <c r="H63">
-        <v>7.3704000000000006E-2</v>
+        <v>0.07370400000000001</v>
       </c>
       <c r="I63">
-        <v>1.2540009102522561E-9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.254000910252256E-09</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>71</v>
       </c>
       <c r="B64">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C64">
         <v>250</v>
@@ -2946,21 +3077,21 @@
         <v>100000</v>
       </c>
       <c r="G64">
-        <v>83.447903219535732</v>
+        <v>83.44790321953573</v>
       </c>
       <c r="H64">
         <v>1.429236</v>
       </c>
       <c r="I64">
-        <v>2.4269474047850029E-8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.426947404785003E-08</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>72</v>
       </c>
       <c r="B65">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C65">
         <v>500</v>
@@ -2975,21 +3106,21 @@
         <v>100000</v>
       </c>
       <c r="G65">
-        <v>74.747772041404332</v>
+        <v>74.74777204140433</v>
       </c>
       <c r="H65">
-        <v>16.528787999999999</v>
+        <v>16.528788</v>
       </c>
       <c r="I65">
-        <v>2.8077047670450168E-7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.807704767045017E-07</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>73</v>
       </c>
       <c r="B66">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C66">
         <v>1000</v>
@@ -3004,16 +3135,16 @@
         <v>100000</v>
       </c>
       <c r="G66">
-        <v>59.312229797827918</v>
+        <v>59.31222979782792</v>
       </c>
       <c r="H66">
-        <v>22.089887999999998</v>
+        <v>22.089888</v>
       </c>
       <c r="I66">
-        <v>3.7547179814316289E-7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.754717981431629E-07</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -3033,16 +3164,16 @@
         <v>100000</v>
       </c>
       <c r="G67">
-        <v>46.002508230130111</v>
+        <v>46.00250823013011</v>
       </c>
       <c r="H67">
-        <v>6.8376000000000006E-2</v>
+        <v>0.06837600000000001</v>
       </c>
       <c r="I67">
-        <v>1.162849113270256E-9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.162849113270256E-09</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -3062,16 +3193,16 @@
         <v>100000</v>
       </c>
       <c r="G68">
-        <v>43.740129739264979</v>
+        <v>43.74012973926498</v>
       </c>
       <c r="H68">
         <v>0.245088</v>
       </c>
       <c r="I68">
-        <v>4.168519410604581E-9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.168519410604581E-09</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -3091,16 +3222,16 @@
         <v>100000</v>
       </c>
       <c r="G69">
-        <v>49.336194000622832</v>
+        <v>49.33619400062283</v>
       </c>
       <c r="H69">
-        <v>0.27661200000000002</v>
+        <v>0.276612</v>
       </c>
       <c r="I69">
-        <v>4.7036132203369941E-9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.703613220336994E-09</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -3120,16 +3251,16 @@
         <v>100000</v>
       </c>
       <c r="G70">
-        <v>40.156128913305878</v>
+        <v>40.15612891330588</v>
       </c>
       <c r="H70">
         <v>0.104784</v>
       </c>
       <c r="I70">
-        <v>1.7824538512196999E-9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.7824538512197E-09</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -3149,16 +3280,16 @@
         <v>100000</v>
       </c>
       <c r="G71">
-        <v>40.286403514506489</v>
+        <v>40.28640351450649</v>
       </c>
       <c r="H71">
-        <v>6.9264000000000006E-2</v>
+        <v>0.06926400000000001</v>
       </c>
       <c r="I71">
-        <v>1.1782259402694451E-9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.178225940269445E-09</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3178,16 +3309,16 @@
         <v>100000</v>
       </c>
       <c r="G72">
-        <v>49.841776073214128</v>
+        <v>49.84177607321413</v>
       </c>
       <c r="H72">
         <v>1.185036</v>
       </c>
       <c r="I72">
-        <v>2.0150376668119951E-8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.015037666811995E-08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -3207,16 +3338,16 @@
         <v>100000</v>
       </c>
       <c r="G73">
-        <v>41.812443755624443</v>
+        <v>41.81244375562444</v>
       </c>
       <c r="H73">
-        <v>6.0384000000000007E-2</v>
+        <v>0.06038400000000001</v>
       </c>
       <c r="I73">
-        <v>1.0271073422533739E-9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.027107342253374E-09</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3236,16 +3367,16 @@
         <v>100000</v>
       </c>
       <c r="G74">
-        <v>43.003393963551517</v>
+        <v>43.00339396355152</v>
       </c>
       <c r="H74">
-        <v>7.7256000000000019E-2</v>
+        <v>0.07725600000000002</v>
       </c>
       <c r="I74">
-        <v>1.314029331564835E-9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.314029331564835E-09</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3265,16 +3396,16 @@
         <v>100000</v>
       </c>
       <c r="G75">
-        <v>46.052442293859933</v>
+        <v>46.05244229385993</v>
       </c>
       <c r="H75">
-        <v>5.7720000000000007E-2</v>
+        <v>0.05772000000000001</v>
       </c>
       <c r="I75">
-        <v>9.8162387418013493E-10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.816238741801349E-10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -3297,13 +3428,13 @@
         <v>67.93838431895503</v>
       </c>
       <c r="H76">
-        <v>6.5268000000000007E-2</v>
+        <v>0.06526800000000001</v>
       </c>
       <c r="I76">
-        <v>1.108999408633842E-9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.108999408633842E-09</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -3323,16 +3454,16 @@
         <v>100000</v>
       </c>
       <c r="G77">
-        <v>69.967110930430195</v>
+        <v>69.9671109304302</v>
       </c>
       <c r="H77">
-        <v>2.4388920000000001</v>
+        <v>2.438892</v>
       </c>
       <c r="I77">
-        <v>4.1436937557741912E-8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.143693755774191E-08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -3352,21 +3483,21 @@
         <v>100000</v>
       </c>
       <c r="G78">
-        <v>75.417978572992567</v>
+        <v>75.41797857299257</v>
       </c>
       <c r="H78">
-        <v>8.5461120000000008</v>
+        <v>8.546112000000001</v>
       </c>
       <c r="I78">
-        <v>1.451667466652781E-7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.451667466652781E-07</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>86</v>
       </c>
       <c r="B79">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C79">
         <v>25</v>
@@ -3381,21 +3512,21 @@
         <v>100000</v>
       </c>
       <c r="G79">
-        <v>42.875225658712708</v>
+        <v>42.87522565871271</v>
       </c>
       <c r="H79">
-        <v>5.3724000000000008E-2</v>
+        <v>0.05372400000000001</v>
       </c>
       <c r="I79">
         <v>9.137837988109473E-10</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>87</v>
       </c>
       <c r="B80">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C80">
         <v>50</v>
@@ -3410,21 +3541,21 @@
         <v>100000</v>
       </c>
       <c r="G80">
-        <v>45.992365398306262</v>
+        <v>45.99236539830626</v>
       </c>
       <c r="H80">
-        <v>5.6832000000000008E-2</v>
+        <v>0.05683200000000001</v>
       </c>
       <c r="I80">
-        <v>9.6652433843422898E-10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.66524338434229E-10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
         <v>88</v>
       </c>
       <c r="B81">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C81">
         <v>100</v>
@@ -3439,21 +3570,21 @@
         <v>100000</v>
       </c>
       <c r="G81">
-        <v>78.257115989027369</v>
+        <v>78.25711598902737</v>
       </c>
       <c r="H81">
-        <v>0.32367600000000007</v>
+        <v>0.3236760000000001</v>
       </c>
       <c r="I81">
-        <v>5.4974184856267217E-9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.497418485626722E-09</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
         <v>89</v>
       </c>
       <c r="B82">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C82">
         <v>250</v>
@@ -3468,21 +3599,21 @@
         <v>100000</v>
       </c>
       <c r="G82">
-        <v>84.521002804322691</v>
+        <v>84.52100280432269</v>
       </c>
       <c r="H82">
-        <v>1.5801959999999999</v>
+        <v>1.580196</v>
       </c>
       <c r="I82">
-        <v>2.6831711983487429E-8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.683171198348743E-08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>90</v>
       </c>
       <c r="B83">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C83">
         <v>500</v>
@@ -3500,18 +3631,18 @@
         <v>70.38219379471181</v>
       </c>
       <c r="H83">
-        <v>13.723152000000001</v>
+        <v>13.723152</v>
       </c>
       <c r="I83">
-        <v>2.33153320476307E-7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.33153320476307E-07</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>91</v>
       </c>
       <c r="B84">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C84">
         <v>1000</v>
@@ -3526,16 +3657,16 @@
         <v>100000</v>
       </c>
       <c r="G84">
-        <v>59.844632121878881</v>
+        <v>59.84463212187888</v>
       </c>
       <c r="H84">
-        <v>18.893975999999999</v>
+        <v>18.893976</v>
       </c>
       <c r="I84">
-        <v>3.2114246436645188E-7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.211424643664519E-07</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -3555,16 +3686,16 @@
         <v>100000</v>
       </c>
       <c r="G85">
-        <v>62.066127482309447</v>
+        <v>62.06612748230945</v>
       </c>
       <c r="H85">
-        <v>8.2140000000000005E-2</v>
+        <v>0.08214</v>
       </c>
       <c r="I85">
-        <v>1.3960138283630641E-9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.396013828363064E-09</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -3584,16 +3715,16 @@
         <v>100000</v>
       </c>
       <c r="G86">
-        <v>77.833062179468229</v>
+        <v>77.83306217946823</v>
       </c>
       <c r="H86">
-        <v>0.43201200000000012</v>
+        <v>0.4320120000000001</v>
       </c>
       <c r="I86">
-        <v>7.3375591875757201E-9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.33755918757572E-09</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3616,13 +3747,13 @@
         <v>81.25600674201732</v>
       </c>
       <c r="H87">
-        <v>0.81518400000000002</v>
+        <v>0.815184</v>
       </c>
       <c r="I87">
-        <v>1.384365798467051E-8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.384365798467051E-08</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -3642,16 +3773,16 @@
         <v>100000</v>
       </c>
       <c r="G88">
-        <v>78.549875117020378</v>
+        <v>78.54987511702038</v>
       </c>
       <c r="H88">
-        <v>5.4509880000000006</v>
+        <v>5.450988000000001</v>
       </c>
       <c r="I88">
-        <v>9.2580248751973959E-8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.258024875197396E-08</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
         <v>96</v>
       </c>
@@ -3671,16 +3802,16 @@
         <v>100000</v>
       </c>
       <c r="G89">
-        <v>56.286619538058282</v>
+        <v>56.28661953805828</v>
       </c>
       <c r="H89">
         <v>26.047704</v>
       </c>
       <c r="I89">
-        <v>4.4279923644286663E-7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.427992364428666E-07</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -3700,16 +3831,16 @@
         <v>100000</v>
       </c>
       <c r="G90">
-        <v>53.358238959302312</v>
+        <v>53.35823895930231</v>
       </c>
       <c r="H90">
-        <v>28.393356000000001</v>
+        <v>28.393356</v>
       </c>
       <c r="I90">
-        <v>4.8273193827436104E-7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.82731938274361E-07</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
         <v>98</v>
       </c>
@@ -3729,16 +3860,16 @@
         <v>100000</v>
       </c>
       <c r="G91">
-        <v>84.094911262439254</v>
+        <v>84.09491126243925</v>
       </c>
       <c r="H91">
-        <v>0.87956400000000001</v>
+        <v>0.879564</v>
       </c>
       <c r="I91">
-        <v>1.4935247097114419E-8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.493524709711442E-08</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -3758,16 +3889,16 @@
         <v>100000</v>
       </c>
       <c r="G92">
-        <v>76.321864356853624</v>
+        <v>76.32186435685362</v>
       </c>
       <c r="H92">
-        <v>0.83516400000000002</v>
+        <v>0.835164</v>
       </c>
       <c r="I92">
-        <v>1.41858161348848E-8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.41858161348848E-08</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
         <v>100</v>
       </c>
@@ -3787,16 +3918,16 @@
         <v>100000</v>
       </c>
       <c r="G93">
-        <v>82.044579524548197</v>
+        <v>82.0445795245482</v>
       </c>
       <c r="H93">
-        <v>1.4514359999999999</v>
+        <v>1.451436</v>
       </c>
       <c r="I93">
-        <v>2.4647855935536039E-8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.464785593553604E-08</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -3816,16 +3947,16 @@
         <v>50000</v>
       </c>
       <c r="G94">
-        <v>62.848420189591081</v>
+        <v>62.84842018959108</v>
       </c>
       <c r="H94">
         <v>13.372836</v>
       </c>
       <c r="I94">
-        <v>2.2727134523758549E-7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.272713452375855E-07</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -3845,16 +3976,16 @@
         <v>50000</v>
       </c>
       <c r="G95">
-        <v>53.705572759337613</v>
+        <v>53.70557275933761</v>
       </c>
       <c r="H95">
         <v>18.327876</v>
       </c>
       <c r="I95">
-        <v>3.1159844989378228E-7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.115984498937823E-07</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -3874,16 +4005,16 @@
         <v>50000</v>
       </c>
       <c r="G96">
-        <v>51.875641954753327</v>
+        <v>51.87564195475333</v>
       </c>
       <c r="H96">
-        <v>17.771100000000001</v>
+        <v>17.7711</v>
       </c>
       <c r="I96">
-        <v>3.0215507288971728E-7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.021550728897173E-07</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -3903,16 +4034,16 @@
         <v>50000</v>
       </c>
       <c r="G97">
-        <v>83.565813000571481</v>
+        <v>83.56581300057148</v>
       </c>
       <c r="H97">
         <v>2.103672</v>
       </c>
       <c r="I97">
-        <v>3.5721719630219347E-8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.572171963021935E-08</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -3932,16 +4063,16 @@
         <v>50000</v>
       </c>
       <c r="G98">
-        <v>80.090355904080099</v>
+        <v>80.0903559040801</v>
       </c>
       <c r="H98">
-        <v>1.7720039999999999</v>
+        <v>1.772004</v>
       </c>
       <c r="I98">
-        <v>3.0094043578362899E-8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.00940435783629E-08</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -3961,16 +4092,16 @@
         <v>50000</v>
       </c>
       <c r="G99">
-        <v>79.913845230501124</v>
+        <v>79.91384523050112</v>
       </c>
       <c r="H99">
         <v>2.570316</v>
       </c>
       <c r="I99">
-        <v>4.3652135219849121E-8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.365213521984912E-08</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -3990,16 +4121,16 @@
         <v>50000</v>
       </c>
       <c r="G100">
-        <v>54.643085459032761</v>
+        <v>54.64308545903276</v>
       </c>
       <c r="H100">
-        <v>21.567299999999999</v>
+        <v>21.5673</v>
       </c>
       <c r="I100">
-        <v>3.6665897246277312E-7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.666589724627731E-07</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -4019,16 +4150,16 @@
         <v>50000</v>
       </c>
       <c r="G101">
-        <v>51.983151763379553</v>
+        <v>51.98315176337955</v>
       </c>
       <c r="H101">
-        <v>21.561084000000001</v>
+        <v>21.561084</v>
       </c>
       <c r="I101">
-        <v>3.6659308241246752E-7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.665930824124675E-07</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -4048,16 +4179,16 @@
         <v>50000</v>
       </c>
       <c r="G102">
-        <v>50.269058735474758</v>
+        <v>50.26905873547476</v>
       </c>
       <c r="H102">
         <v>19.981776</v>
       </c>
       <c r="I102">
-        <v>3.3976460806111327E-7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.397646080611133E-07</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -4077,16 +4208,16 @@
         <v>50000</v>
       </c>
       <c r="G103">
-        <v>82.451295677753635</v>
+        <v>82.45129567775363</v>
       </c>
       <c r="H103">
         <v>4.000884000000001</v>
       </c>
       <c r="I103">
-        <v>6.7940700000234214E-8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.794070000023421E-08</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
         <v>111</v>
       </c>
@@ -4106,16 +4237,16 @@
         <v>50000</v>
       </c>
       <c r="G104">
-        <v>80.363527821998133</v>
+        <v>80.36352782199813</v>
       </c>
       <c r="H104">
-        <v>2.3660760000000001</v>
+        <v>2.366076</v>
       </c>
       <c r="I104">
-        <v>4.0182754354165728E-8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.018275435416573E-08</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
         <v>112</v>
       </c>
@@ -4135,16 +4266,16 @@
         <v>50000</v>
       </c>
       <c r="G105">
-        <v>68.373940743623749</v>
+        <v>68.37394074362375</v>
       </c>
       <c r="H105">
-        <v>7.6248120000000004</v>
+        <v>7.624812</v>
       </c>
       <c r="I105">
-        <v>1.29554480135715E-7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.29554480135715E-07</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
         <v>113</v>
       </c>
@@ -4170,10 +4301,10 @@
         <v>13.021188</v>
       </c>
       <c r="I106">
-        <v>2.213787212444845E-7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.213787212444845E-07</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -4193,16 +4324,16 @@
         <v>25000</v>
       </c>
       <c r="G107">
-        <v>49.711379629490821</v>
+        <v>49.71137962949082</v>
       </c>
       <c r="H107">
         <v>12.967908</v>
       </c>
       <c r="I107">
-        <v>2.2050774941792229E-7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.205077494179223E-07</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -4222,21 +4353,21 @@
         <v>25000</v>
       </c>
       <c r="G108">
-        <v>49.271561417489217</v>
+        <v>49.27156141748922</v>
       </c>
       <c r="H108">
         <v>12.58074</v>
       </c>
       <c r="I108">
-        <v>2.1392814147983561E-7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.139281414798356E-07</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
         <v>116</v>
       </c>
       <c r="B109">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C109">
         <v>250</v>
@@ -4251,21 +4382,21 @@
         <v>25000</v>
       </c>
       <c r="G109">
-        <v>82.898326350939612</v>
+        <v>82.89832635093961</v>
       </c>
       <c r="H109">
-        <v>1.2947040000000001</v>
+        <v>1.294704</v>
       </c>
       <c r="I109">
-        <v>2.1985514573707641E-8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.198551457370764E-08</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
         <v>117</v>
       </c>
       <c r="B110">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C110">
         <v>250</v>
@@ -4280,21 +4411,21 @@
         <v>50000</v>
       </c>
       <c r="G110">
-        <v>83.611037431161151</v>
+        <v>83.61103743116115</v>
       </c>
       <c r="H110">
-        <v>2.0632679999999999</v>
+        <v>2.063268</v>
       </c>
       <c r="I110">
-        <v>3.5035568842749367E-8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.503556884274937E-08</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B111">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C111">
         <v>250</v>
@@ -4303,27 +4434,27 @@
         <v>250</v>
       </c>
       <c r="E111">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F111">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G111">
-        <v>84.521002804322691</v>
+        <v>85.6186498597537</v>
       </c>
       <c r="H111">
-        <v>1.5801959999999999</v>
+        <v>3.906756000000001</v>
       </c>
       <c r="I111">
-        <v>2.6831711983487429E-8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.633370989206419E-08</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B112">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C112">
         <v>250</v>
@@ -4332,27 +4463,27 @@
         <v>250</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F112">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="G112">
-        <v>85.618649859753702</v>
+        <v>85.97783100570673</v>
       </c>
       <c r="H112">
-        <v>3.906756000000001</v>
+        <v>3.326892</v>
       </c>
       <c r="I112">
-        <v>6.633370989206419E-8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.648723870112017E-08</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B113">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C113">
         <v>250</v>
@@ -4361,53 +4492,53 @@
         <v>250</v>
       </c>
       <c r="E113">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F113">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="G113">
-        <v>85.977831005706733</v>
+        <v>84.91116682837716</v>
       </c>
       <c r="H113">
-        <v>3.326892</v>
+        <v>4.122096</v>
       </c>
       <c r="I113">
-        <v>5.6487238701120171E-8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.999203522047654E-08</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B114">
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="C114">
         <v>250</v>
       </c>
       <c r="D114">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="E114">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F114">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="G114">
-        <v>84.911166828377162</v>
+        <v>50.75039212264029</v>
       </c>
       <c r="H114">
-        <v>4.122096</v>
+        <v>27.008076</v>
       </c>
       <c r="I114">
-        <v>6.9992035220476539E-8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.59228854886644E-07</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B115">
         <v>-1.2</v>
@@ -4416,7 +4547,7 @@
         <v>250</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E115">
         <v>100</v>
@@ -4425,18 +4556,18 @@
         <v>100000</v>
       </c>
       <c r="G115">
-        <v>50.750392122640292</v>
+        <v>50.68773807701082</v>
       </c>
       <c r="H115">
-        <v>27.008075999999999</v>
+        <v>25.946028</v>
       </c>
       <c r="I115">
-        <v>4.5922885488664401E-7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.411715663124783E-07</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B116">
         <v>-1.2</v>
@@ -4445,7 +4576,7 @@
         <v>250</v>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E116">
         <v>100</v>
@@ -4454,18 +4585,18 @@
         <v>100000</v>
       </c>
       <c r="G116">
-        <v>50.68773807701082</v>
+        <v>52.83402977849236</v>
       </c>
       <c r="H116">
-        <v>25.946027999999998</v>
+        <v>27.73002</v>
       </c>
       <c r="I116">
-        <v>4.4117156631247828E-7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.714642621149467E-07</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B117">
         <v>-1.2</v>
@@ -4474,7 +4605,7 @@
         <v>250</v>
       </c>
       <c r="D117">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E117">
         <v>100</v>
@@ -4483,18 +4614,18 @@
         <v>100000</v>
       </c>
       <c r="G117">
-        <v>52.834029778492358</v>
+        <v>55.52404180275892</v>
       </c>
       <c r="H117">
-        <v>27.73002</v>
+        <v>26.005524</v>
       </c>
       <c r="I117">
-        <v>4.7146426211494668E-7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.420959500829483E-07</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B118">
         <v>-1.2</v>
@@ -4503,7 +4634,7 @@
         <v>250</v>
       </c>
       <c r="D118">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E118">
         <v>100</v>
@@ -4512,18 +4643,18 @@
         <v>100000</v>
       </c>
       <c r="G118">
-        <v>55.524041802758923</v>
+        <v>83.55119037626523</v>
       </c>
       <c r="H118">
-        <v>26.005524000000001</v>
+        <v>2.269728</v>
       </c>
       <c r="I118">
-        <v>4.4209595008294829E-7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.8541481547297E-08</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="B119">
         <v>-1.2</v>
@@ -4532,7 +4663,7 @@
         <v>250</v>
       </c>
       <c r="D119">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="E119">
         <v>100</v>
@@ -4541,18 +4672,18 @@
         <v>100000</v>
       </c>
       <c r="G119">
-        <v>78.549875117020378</v>
+        <v>74.07597123296348</v>
       </c>
       <c r="H119">
-        <v>5.4509880000000006</v>
+        <v>2.953044</v>
       </c>
       <c r="I119">
-        <v>9.2580248751973959E-8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.016400963429817E-08</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B120">
         <v>-1.2</v>
@@ -4561,7 +4692,7 @@
         <v>250</v>
       </c>
       <c r="D120">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E120">
         <v>100</v>
@@ -4570,24 +4701,24 @@
         <v>100000</v>
       </c>
       <c r="G120">
-        <v>83.551190376265225</v>
+        <v>55.77466087008303</v>
       </c>
       <c r="H120">
-        <v>2.2697280000000002</v>
+        <v>1.110888</v>
       </c>
       <c r="I120">
-        <v>3.8541481547296997E-8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.888499012765766E-08</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B121">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C121">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D121">
         <v>1000</v>
@@ -4599,27 +4730,27 @@
         <v>100000</v>
       </c>
       <c r="G121">
-        <v>74.075971232963482</v>
+        <v>54.06533446712018</v>
       </c>
       <c r="H121">
-        <v>2.9530439999999998</v>
+        <v>0.05328</v>
       </c>
       <c r="I121">
-        <v>5.0164009634298172E-8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.058180940580698E-10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B122">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C122">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D122">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E122">
         <v>100</v>
@@ -4628,24 +4759,24 @@
         <v>100000</v>
       </c>
       <c r="G122">
-        <v>55.774660870083032</v>
+        <v>52.37346381084352</v>
       </c>
       <c r="H122">
-        <v>1.1108880000000001</v>
+        <v>0.044844</v>
       </c>
       <c r="I122">
-        <v>1.8884990127657659E-8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.624495298201005E-10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B123">
         <v>-0.9</v>
       </c>
       <c r="C123">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D123">
         <v>1000</v>
@@ -4657,24 +4788,24 @@
         <v>100000</v>
       </c>
       <c r="G123">
-        <v>54.065334467120181</v>
+        <v>52.64552588154607</v>
       </c>
       <c r="H123">
-        <v>5.3280000000000001E-2</v>
+        <v>0.040404</v>
       </c>
       <c r="I123">
-        <v>9.0581809405806976E-10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.869518510905723E-10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B124">
         <v>-0.9</v>
       </c>
       <c r="C124">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D124">
         <v>1000</v>
@@ -4686,24 +4817,24 @@
         <v>100000</v>
       </c>
       <c r="G124">
-        <v>52.373463810843518</v>
+        <v>53.52168565717511</v>
       </c>
       <c r="H124">
-        <v>4.4844000000000002E-2</v>
+        <v>0.030636</v>
       </c>
       <c r="I124">
-        <v>7.6244952982010048E-10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.208569578856103E-10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B125">
         <v>-0.9</v>
       </c>
       <c r="C125">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D125">
         <v>1000</v>
@@ -4715,24 +4846,24 @@
         <v>100000</v>
       </c>
       <c r="G125">
-        <v>52.645525881546071</v>
+        <v>51.93895434590224</v>
       </c>
       <c r="H125">
-        <v>4.0404000000000002E-2</v>
+        <v>0.04351200000000001</v>
       </c>
       <c r="I125">
-        <v>6.8695185109057225E-10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.398156312708689E-10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B126">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C126">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D126">
         <v>1000</v>
@@ -4744,24 +4875,24 @@
         <v>100000</v>
       </c>
       <c r="G126">
-        <v>53.521685657175112</v>
+        <v>66.57591741818388</v>
       </c>
       <c r="H126">
-        <v>3.0636E-2</v>
+        <v>0.07192800000000002</v>
       </c>
       <c r="I126">
-        <v>5.2085695788561034E-10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.222230521658508E-09</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B127">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C127">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D127">
         <v>1000</v>
@@ -4773,24 +4904,24 @@
         <v>100000</v>
       </c>
       <c r="G127">
-        <v>51.938954345902239</v>
+        <v>56.83060155301417</v>
       </c>
       <c r="H127">
-        <v>4.3512000000000009E-2</v>
+        <v>0.089688</v>
       </c>
       <c r="I127">
-        <v>7.3981563127086893E-10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.524621768386918E-09</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B128">
         <v>-1</v>
       </c>
       <c r="C128">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D128">
         <v>1000</v>
@@ -4802,24 +4933,24 @@
         <v>100000</v>
       </c>
       <c r="G128">
-        <v>66.575917418183877</v>
+        <v>60.90287086874571</v>
       </c>
       <c r="H128">
-        <v>7.192800000000002E-2</v>
+        <v>0.04440000000000001</v>
       </c>
       <c r="I128">
-        <v>1.222230521658508E-9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.546378757634915E-10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B129">
         <v>-1</v>
       </c>
       <c r="C129">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D129">
         <v>1000</v>
@@ -4831,24 +4962,24 @@
         <v>100000</v>
       </c>
       <c r="G129">
-        <v>56.830601553014169</v>
+        <v>86.1331473966909</v>
       </c>
       <c r="H129">
-        <v>8.9688000000000004E-2</v>
+        <v>0.6105</v>
       </c>
       <c r="I129">
-        <v>1.5246217683869181E-9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.036560278103142E-08</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B130">
         <v>-1</v>
       </c>
       <c r="C130">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D130">
         <v>1000</v>
@@ -4860,170 +4991,170 @@
         <v>100000</v>
       </c>
       <c r="G130">
-        <v>60.902870868745708</v>
+        <v>88.37986809316276</v>
       </c>
       <c r="H130">
-        <v>4.4400000000000009E-2</v>
+        <v>1.415028</v>
       </c>
       <c r="I130">
-        <v>7.5463787576349147E-10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.402338319558451E-08</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B131">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C131">
+        <v>50</v>
+      </c>
+      <c r="D131">
+        <v>1000</v>
+      </c>
+      <c r="E131">
+        <v>100</v>
+      </c>
+      <c r="F131">
+        <v>100000</v>
+      </c>
+      <c r="G131">
+        <v>59.64206893961653</v>
+      </c>
+      <c r="H131">
+        <v>0.034188</v>
+      </c>
+      <c r="I131">
+        <v>5.811010501729644E-10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132">
+        <v>-1.1</v>
+      </c>
+      <c r="C132">
+        <v>100</v>
+      </c>
+      <c r="D132">
+        <v>1000</v>
+      </c>
+      <c r="E132">
+        <v>100</v>
+      </c>
+      <c r="F132">
+        <v>100000</v>
+      </c>
+      <c r="G132">
+        <v>76.85055454438319</v>
+      </c>
+      <c r="H132">
+        <v>0.080808</v>
+      </c>
+      <c r="I132">
+        <v>1.372548056053983E-09</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133">
+        <v>-1.1</v>
+      </c>
+      <c r="C133">
+        <v>250</v>
+      </c>
+      <c r="D133">
+        <v>1000</v>
+      </c>
+      <c r="E133">
+        <v>100</v>
+      </c>
+      <c r="F133">
+        <v>100000</v>
+      </c>
+      <c r="G133">
+        <v>86.56921463031729</v>
+      </c>
+      <c r="H133">
+        <v>1.300476</v>
+      </c>
+      <c r="I133">
+        <v>2.208022622552924E-08</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134">
+        <v>-1.1</v>
+      </c>
+      <c r="C134">
         <v>500</v>
       </c>
-      <c r="D131">
-        <v>1000</v>
-      </c>
-      <c r="E131">
-        <v>100</v>
-      </c>
-      <c r="F131">
-        <v>100000</v>
-      </c>
-      <c r="G131">
-        <v>86.133147396690902</v>
-      </c>
-      <c r="H131">
-        <v>0.61050000000000004</v>
-      </c>
-      <c r="I131">
-        <v>1.0365602781031419E-8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132">
-        <v>-1</v>
-      </c>
-      <c r="C132">
-        <v>1000</v>
-      </c>
-      <c r="D132">
-        <v>1000</v>
-      </c>
-      <c r="E132">
-        <v>100</v>
-      </c>
-      <c r="F132">
-        <v>100000</v>
-      </c>
-      <c r="G132">
-        <v>88.379868093162756</v>
-      </c>
-      <c r="H132">
-        <v>1.415028</v>
-      </c>
-      <c r="I132">
-        <v>2.4023383195584509E-8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>138</v>
-      </c>
-      <c r="B133">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C133">
+      <c r="D134">
+        <v>1000</v>
+      </c>
+      <c r="E134">
+        <v>100</v>
+      </c>
+      <c r="F134">
+        <v>100000</v>
+      </c>
+      <c r="G134">
+        <v>84.4288200639247</v>
+      </c>
+      <c r="H134">
+        <v>2.105892</v>
+      </c>
+      <c r="I134">
+        <v>3.575815903866583E-08</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135">
+        <v>-1.1</v>
+      </c>
+      <c r="C135">
+        <v>1000</v>
+      </c>
+      <c r="D135">
+        <v>1000</v>
+      </c>
+      <c r="E135">
+        <v>100</v>
+      </c>
+      <c r="F135">
+        <v>100000</v>
+      </c>
+      <c r="G135">
+        <v>82.61197456153826</v>
+      </c>
+      <c r="H135">
+        <v>3.996888</v>
+      </c>
+      <c r="I135">
+        <v>6.787239777277621E-08</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136">
+        <v>-1.2</v>
+      </c>
+      <c r="C136">
         <v>50</v>
       </c>
-      <c r="D133">
-        <v>1000</v>
-      </c>
-      <c r="E133">
-        <v>100</v>
-      </c>
-      <c r="F133">
-        <v>100000</v>
-      </c>
-      <c r="G133">
-        <v>59.642068939616529</v>
-      </c>
-      <c r="H133">
-        <v>3.4188000000000003E-2</v>
-      </c>
-      <c r="I133">
-        <v>5.8110105017296441E-10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>139</v>
-      </c>
-      <c r="B134">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C134">
-        <v>100</v>
-      </c>
-      <c r="D134">
-        <v>1000</v>
-      </c>
-      <c r="E134">
-        <v>100</v>
-      </c>
-      <c r="F134">
-        <v>100000</v>
-      </c>
-      <c r="G134">
-        <v>76.850554544383186</v>
-      </c>
-      <c r="H134">
-        <v>8.0808000000000005E-2</v>
-      </c>
-      <c r="I134">
-        <v>1.3725480560539831E-9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>140</v>
-      </c>
-      <c r="B135">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C135">
-        <v>250</v>
-      </c>
-      <c r="D135">
-        <v>1000</v>
-      </c>
-      <c r="E135">
-        <v>100</v>
-      </c>
-      <c r="F135">
-        <v>100000</v>
-      </c>
-      <c r="G135">
-        <v>86.56921463031729</v>
-      </c>
-      <c r="H135">
-        <v>1.300476</v>
-      </c>
-      <c r="I135">
-        <v>2.2080226225529241E-8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C136">
-        <v>500</v>
-      </c>
       <c r="D136">
         <v>1000</v>
       </c>
@@ -5034,24 +5165,24 @@
         <v>100000</v>
       </c>
       <c r="G136">
-        <v>84.428820063924704</v>
+        <v>69.02674196735026</v>
       </c>
       <c r="H136">
-        <v>2.1058919999999999</v>
+        <v>0.17538</v>
       </c>
       <c r="I136">
-        <v>3.5758159038665832E-8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.979832144302711E-09</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B137">
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="C137">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D137">
         <v>1000</v>
@@ -5063,24 +5194,24 @@
         <v>100000</v>
       </c>
       <c r="G137">
-        <v>82.611974561538261</v>
+        <v>82.41764714763009</v>
       </c>
       <c r="H137">
-        <v>3.9968880000000002</v>
+        <v>1.477188</v>
       </c>
       <c r="I137">
-        <v>6.7872397772776214E-8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.508478735785043E-08</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B138">
         <v>-1.2</v>
       </c>
       <c r="C138">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D138">
         <v>1000</v>
@@ -5092,24 +5223,24 @@
         <v>100000</v>
       </c>
       <c r="G138">
-        <v>69.026741967350262</v>
+        <v>78.02943952889554</v>
       </c>
       <c r="H138">
-        <v>0.17538000000000001</v>
+        <v>2.485512</v>
       </c>
       <c r="I138">
-        <v>2.9798321443027111E-9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.221513620374384E-08</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B139">
         <v>-1.2</v>
       </c>
       <c r="C139">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D139">
         <v>1000</v>
@@ -5121,82 +5252,82 @@
         <v>100000</v>
       </c>
       <c r="G139">
-        <v>82.417647147630092</v>
+        <v>83.20632519887992</v>
       </c>
       <c r="H139">
-        <v>1.4771879999999999</v>
+        <v>2.851812000000001</v>
       </c>
       <c r="I139">
-        <v>2.5084787357850431E-8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.842633318546048E-08</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B140">
         <v>-1.2</v>
       </c>
       <c r="C140">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D140">
         <v>1000</v>
       </c>
       <c r="E140">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F140">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G140">
-        <v>78.029439528895537</v>
+        <v>61.76195726258415</v>
       </c>
       <c r="H140">
-        <v>2.4855119999999999</v>
+        <v>16.6056</v>
       </c>
       <c r="I140">
-        <v>4.2215136203743838E-8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.822246754808454E-07</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B141">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C141">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D141">
         <v>1000</v>
       </c>
       <c r="E141">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F141">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G141">
-        <v>83.206325198879924</v>
+        <v>78.57444522214966</v>
       </c>
       <c r="H141">
-        <v>2.8518120000000011</v>
+        <v>0.75258</v>
       </c>
       <c r="I141">
-        <v>4.8426333185460481E-8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.278189822204737E-08</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B142">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C142">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D142">
         <v>1000</v>
@@ -5208,24 +5339,24 @@
         <v>50000</v>
       </c>
       <c r="G142">
-        <v>61.761957262584147</v>
+        <v>77.79132700804179</v>
       </c>
       <c r="H142">
-        <v>16.605599999999999</v>
+        <v>2.408700000000001</v>
       </c>
       <c r="I142">
-        <v>2.8222467548084542E-7</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.091092118528711E-08</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B143">
         <v>-1.3</v>
       </c>
       <c r="C143">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D143">
         <v>1000</v>
@@ -5237,24 +5368,24 @@
         <v>50000</v>
       </c>
       <c r="G143">
-        <v>78.574445222149663</v>
+        <v>79.85544611488123</v>
       </c>
       <c r="H143">
-        <v>0.75258000000000003</v>
+        <v>2.136084</v>
       </c>
       <c r="I143">
-        <v>1.278189822204737E-8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.627758204132035E-08</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B144">
         <v>-1.3</v>
       </c>
       <c r="C144">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D144">
         <v>1000</v>
@@ -5266,24 +5397,24 @@
         <v>50000</v>
       </c>
       <c r="G144">
-        <v>77.79132700804179</v>
+        <v>72.83990739282002</v>
       </c>
       <c r="H144">
-        <v>2.408700000000001</v>
+        <v>3.320232</v>
       </c>
       <c r="I144">
-        <v>4.0910921185287107E-8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.640435557526038E-08</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B145">
         <v>-1.3</v>
       </c>
       <c r="C145">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D145">
         <v>1000</v>
@@ -5295,24 +5426,24 @@
         <v>50000</v>
       </c>
       <c r="G145">
-        <v>79.855446114881232</v>
+        <v>60.10208323188664</v>
       </c>
       <c r="H145">
-        <v>2.1360839999999999</v>
+        <v>10.838928</v>
       </c>
       <c r="I145">
-        <v>3.6277582041320353E-8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.842282160677826E-07</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B146">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="C146">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D146">
         <v>1000</v>
@@ -5324,24 +5455,24 @@
         <v>50000</v>
       </c>
       <c r="G146">
-        <v>72.839907392820024</v>
+        <v>76.93564941897037</v>
       </c>
       <c r="H146">
-        <v>3.3202319999999999</v>
+        <v>1.890552</v>
       </c>
       <c r="I146">
-        <v>5.6404355575260379E-8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.211147994289137E-08</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B147">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="C147">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D147">
         <v>1000</v>
@@ -5353,24 +5484,24 @@
         <v>50000</v>
       </c>
       <c r="G147">
-        <v>60.102083231886638</v>
+        <v>80.27530181702622</v>
       </c>
       <c r="H147">
-        <v>10.838927999999999</v>
+        <v>3.161724</v>
       </c>
       <c r="I147">
-        <v>1.8422821606778261E-7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.369533171743946E-08</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B148">
         <v>-1.4</v>
       </c>
       <c r="C148">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D148">
         <v>1000</v>
@@ -5382,82 +5513,82 @@
         <v>50000</v>
       </c>
       <c r="G148">
-        <v>76.935649418970371</v>
+        <v>71.45711837115508</v>
       </c>
       <c r="H148">
-        <v>1.890552</v>
+        <v>2.441556</v>
       </c>
       <c r="I148">
-        <v>3.2111479942891367E-8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.147967892342157E-08</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B149">
         <v>-1.4</v>
       </c>
       <c r="C149">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D149">
         <v>1000</v>
       </c>
       <c r="E149">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F149">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G149">
-        <v>80.275301817026218</v>
+        <v>62.11432785148533</v>
       </c>
       <c r="H149">
-        <v>3.161724</v>
+        <v>9.943380000000001</v>
       </c>
       <c r="I149">
-        <v>5.3695331717439462E-8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.689928011889892E-07</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B150">
         <v>-1.4</v>
       </c>
       <c r="C150">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D150">
         <v>1000</v>
       </c>
       <c r="E150">
+        <v>25</v>
+      </c>
+      <c r="F150">
+        <v>25000</v>
+      </c>
+      <c r="G150">
+        <v>54.75736632020758</v>
+      </c>
+      <c r="H150">
+        <v>21.40746</v>
+      </c>
+      <c r="I150">
+        <v>3.639398852432184E-07</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151">
+        <v>-1.5</v>
+      </c>
+      <c r="C151">
         <v>50</v>
-      </c>
-      <c r="F150">
-        <v>50000</v>
-      </c>
-      <c r="G150">
-        <v>71.457118371155076</v>
-      </c>
-      <c r="H150">
-        <v>2.4415559999999998</v>
-      </c>
-      <c r="I150">
-        <v>4.1479678923421569E-8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>156</v>
-      </c>
-      <c r="B151">
-        <v>-1.4</v>
-      </c>
-      <c r="C151">
-        <v>500</v>
       </c>
       <c r="D151">
         <v>1000</v>
@@ -5469,24 +5600,24 @@
         <v>25000</v>
       </c>
       <c r="G151">
-        <v>62.114327851485328</v>
+        <v>79.08558168789266</v>
       </c>
       <c r="H151">
-        <v>9.9433800000000012</v>
+        <v>3.113772</v>
       </c>
       <c r="I151">
-        <v>1.689928011889892E-7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.288353076331398E-08</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B152">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="C152">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D152">
         <v>1000</v>
@@ -5498,24 +5629,24 @@
         <v>25000</v>
       </c>
       <c r="G152">
-        <v>54.757366320207581</v>
+        <v>79.18485271012059</v>
       </c>
       <c r="H152">
-        <v>21.40746</v>
+        <v>3.597288000000001</v>
       </c>
       <c r="I152">
-        <v>3.6393988524321839E-7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.109519927663253E-08</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B153">
         <v>-1.5</v>
       </c>
       <c r="C153">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D153">
         <v>1000</v>
@@ -5527,24 +5658,24 @@
         <v>25000</v>
       </c>
       <c r="G153">
-        <v>79.085581687892656</v>
+        <v>74.08551063754184</v>
       </c>
       <c r="H153">
-        <v>3.113772</v>
+        <v>1.92474</v>
       </c>
       <c r="I153">
-        <v>5.2883530763313979E-8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.269597010838225E-08</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B154">
         <v>-1.5</v>
       </c>
       <c r="C154">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D154">
         <v>1000</v>
@@ -5556,111 +5687,111 @@
         <v>25000</v>
       </c>
       <c r="G154">
-        <v>79.184852710120595</v>
+        <v>58.64123529488121</v>
       </c>
       <c r="H154">
-        <v>3.5972880000000012</v>
+        <v>14.632908</v>
       </c>
       <c r="I154">
-        <v>6.1095199276632529E-8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.487289511827858E-07</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B155">
         <v>-1.5</v>
       </c>
       <c r="C155">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D155">
         <v>1000</v>
       </c>
       <c r="E155">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F155">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="G155">
-        <v>74.085510637541844</v>
+        <v>53.10889221708681</v>
       </c>
       <c r="H155">
-        <v>1.9247399999999999</v>
+        <v>6.506820000000001</v>
       </c>
       <c r="I155">
-        <v>3.2695970108382247E-8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.106273520076047E-07</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B156">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="C156">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="D156">
         <v>1000</v>
       </c>
       <c r="E156">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F156">
-        <v>25000</v>
+        <v>100000</v>
       </c>
       <c r="G156">
-        <v>58.641235294881213</v>
+        <v>87.78189271282976</v>
       </c>
       <c r="H156">
-        <v>14.632908</v>
+        <v>0.784104</v>
       </c>
       <c r="I156">
-        <v>2.4872895118278578E-7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.331230889061322E-08</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B157">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="C157">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="D157">
         <v>1000</v>
       </c>
       <c r="E157">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F157">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="G157">
-        <v>53.108892217086812</v>
+        <v>87.53045799073361</v>
       </c>
       <c r="H157">
-        <v>6.5068200000000012</v>
+        <v>0.8147400000000001</v>
       </c>
       <c r="I157">
-        <v>1.106273520076047E-7</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.383258045585301E-08</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B158">
         <v>-1</v>
       </c>
       <c r="C158">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D158">
         <v>1000</v>
@@ -5672,112 +5803,112 @@
         <v>100000</v>
       </c>
       <c r="G158">
-        <v>88.379868093162756</v>
+        <v>89.10805588510702</v>
       </c>
       <c r="H158">
-        <v>1.415028</v>
+        <v>2.192916</v>
       </c>
       <c r="I158">
-        <v>2.4023383195584509E-8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.722873212026699E-08</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B159">
         <v>-1</v>
       </c>
       <c r="C159">
+        <v>1250</v>
+      </c>
+      <c r="D159">
+        <v>1000</v>
+      </c>
+      <c r="E159">
+        <v>100</v>
+      </c>
+      <c r="F159">
+        <v>100000</v>
+      </c>
+      <c r="G159">
+        <v>82.13219103219161</v>
+      </c>
+      <c r="H159">
+        <v>5.517588000000001</v>
+      </c>
+      <c r="I159">
+        <v>9.369770939510034E-08</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160">
+        <v>-0.9</v>
+      </c>
+      <c r="C160">
         <v>1100</v>
       </c>
-      <c r="D159">
-        <v>1000</v>
-      </c>
-      <c r="E159">
-        <v>100</v>
-      </c>
-      <c r="F159">
-        <v>100000</v>
-      </c>
-      <c r="G159">
-        <v>87.781892712829759</v>
-      </c>
-      <c r="H159">
-        <v>0.78410400000000002</v>
-      </c>
-      <c r="I159">
-        <v>1.331230889061322E-8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>164</v>
-      </c>
-      <c r="B160">
-        <v>-1</v>
-      </c>
-      <c r="C160">
+      <c r="D160">
+        <v>1000</v>
+      </c>
+      <c r="E160">
+        <v>100</v>
+      </c>
+      <c r="F160">
+        <v>100000</v>
+      </c>
+      <c r="G160">
+        <v>43.3106280135942</v>
+      </c>
+      <c r="H160">
+        <v>0.05727600000000001</v>
+      </c>
+      <c r="I160">
+        <v>9.741819417945698E-10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161">
+        <v>-0.9</v>
+      </c>
+      <c r="C161">
         <v>1250</v>
       </c>
-      <c r="D160">
-        <v>1000</v>
-      </c>
-      <c r="E160">
-        <v>100</v>
-      </c>
-      <c r="F160">
-        <v>100000</v>
-      </c>
-      <c r="G160">
-        <v>87.530457990733609</v>
-      </c>
-      <c r="H160">
-        <v>0.81474000000000013</v>
-      </c>
-      <c r="I160">
-        <v>1.3832580455853009E-8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>165</v>
-      </c>
-      <c r="B161">
-        <v>-1</v>
-      </c>
-      <c r="C161">
+      <c r="D161">
+        <v>1000</v>
+      </c>
+      <c r="E161">
+        <v>100</v>
+      </c>
+      <c r="F161">
+        <v>100000</v>
+      </c>
+      <c r="G161">
+        <v>44.56319206137276</v>
+      </c>
+      <c r="H161">
+        <v>0.112332</v>
+      </c>
+      <c r="I161">
+        <v>1.910507208736988E-09</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162">
+        <v>-0.9</v>
+      </c>
+      <c r="C162">
         <v>1500</v>
       </c>
-      <c r="D161">
-        <v>1000</v>
-      </c>
-      <c r="E161">
-        <v>100</v>
-      </c>
-      <c r="F161">
-        <v>100000</v>
-      </c>
-      <c r="G161">
-        <v>89.108055885107021</v>
-      </c>
-      <c r="H161">
-        <v>2.1929159999999999</v>
-      </c>
-      <c r="I161">
-        <v>3.7228732120266988E-8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>166</v>
-      </c>
-      <c r="B162">
-        <v>-1</v>
-      </c>
-      <c r="C162">
-        <v>1250</v>
-      </c>
       <c r="D162">
         <v>1000</v>
       </c>
@@ -5788,231 +5919,231 @@
         <v>100000</v>
       </c>
       <c r="G162">
-        <v>82.132191032191614</v>
+        <v>54.44425547704819</v>
       </c>
       <c r="H162">
-        <v>5.5175880000000008</v>
+        <v>0.05372400000000001</v>
       </c>
       <c r="I162">
-        <v>9.3697709395100344E-8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.133524568613958E-10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B163">
         <v>-0.9</v>
       </c>
       <c r="C163">
+        <v>1750</v>
+      </c>
+      <c r="D163">
+        <v>1000</v>
+      </c>
+      <c r="E163">
+        <v>100</v>
+      </c>
+      <c r="F163">
+        <v>100000</v>
+      </c>
+      <c r="G163">
+        <v>36.26925394348572</v>
+      </c>
+      <c r="H163">
+        <v>0.029304</v>
+      </c>
+      <c r="I163">
+        <v>4.98561970868169E-10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164">
+        <v>-1.1</v>
+      </c>
+      <c r="C164">
         <v>1100</v>
       </c>
-      <c r="D163">
-        <v>1000</v>
-      </c>
-      <c r="E163">
-        <v>100</v>
-      </c>
-      <c r="F163">
-        <v>100000</v>
-      </c>
-      <c r="G163">
-        <v>43.310628013594197</v>
-      </c>
-      <c r="H163">
-        <v>5.7276000000000007E-2</v>
-      </c>
-      <c r="I163">
-        <v>9.7418194179456979E-10</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>168</v>
-      </c>
-      <c r="B164">
+      <c r="D164">
+        <v>1000</v>
+      </c>
+      <c r="E164">
+        <v>100</v>
+      </c>
+      <c r="F164">
+        <v>100000</v>
+      </c>
+      <c r="G164">
+        <v>76.45517639433409</v>
+      </c>
+      <c r="H164">
+        <v>10.812732</v>
+      </c>
+      <c r="I164">
+        <v>1.836604481053716E-07</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165">
+        <v>-1.1</v>
+      </c>
+      <c r="C165">
+        <v>1250</v>
+      </c>
+      <c r="D165">
+        <v>1000</v>
+      </c>
+      <c r="E165">
+        <v>100</v>
+      </c>
+      <c r="F165">
+        <v>100000</v>
+      </c>
+      <c r="G165">
+        <v>73.510022048059</v>
+      </c>
+      <c r="H165">
+        <v>14.124972</v>
+      </c>
+      <c r="I165">
+        <v>2.399495506522188E-07</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166">
+        <v>-1.1</v>
+      </c>
+      <c r="C166">
+        <v>1500</v>
+      </c>
+      <c r="D166">
+        <v>1000</v>
+      </c>
+      <c r="E166">
+        <v>100</v>
+      </c>
+      <c r="F166">
+        <v>100000</v>
+      </c>
+      <c r="G166">
+        <v>66.65351408231179</v>
+      </c>
+      <c r="H166">
+        <v>18.33498</v>
+      </c>
+      <c r="I166">
+        <v>3.115546276057171E-07</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167">
+        <v>-1.1</v>
+      </c>
+      <c r="C167">
+        <v>1750</v>
+      </c>
+      <c r="D167">
+        <v>1000</v>
+      </c>
+      <c r="E167">
+        <v>100</v>
+      </c>
+      <c r="F167">
+        <v>100000</v>
+      </c>
+      <c r="G167">
+        <v>68.5978932328055</v>
+      </c>
+      <c r="H167">
+        <v>9.888324000000001</v>
+      </c>
+      <c r="I167">
+        <v>1.680126639040281E-07</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168">
         <v>-0.9</v>
       </c>
-      <c r="C164">
-        <v>1250</v>
-      </c>
-      <c r="D164">
-        <v>1000</v>
-      </c>
-      <c r="E164">
-        <v>100</v>
-      </c>
-      <c r="F164">
-        <v>100000</v>
-      </c>
-      <c r="G164">
-        <v>44.56319206137276</v>
-      </c>
-      <c r="H164">
-        <v>0.112332</v>
-      </c>
-      <c r="I164">
-        <v>1.9105072087369879E-9</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>169</v>
-      </c>
-      <c r="B165">
+      <c r="C168">
+        <v>100</v>
+      </c>
+      <c r="D168">
+        <v>1500</v>
+      </c>
+      <c r="E168">
+        <v>100</v>
+      </c>
+      <c r="F168">
+        <v>100000</v>
+      </c>
+      <c r="G168">
+        <v>43.00339396355152</v>
+      </c>
+      <c r="H168">
+        <v>0.025752</v>
+      </c>
+      <c r="I168">
+        <v>4.380097771882782E-10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169">
         <v>-0.9</v>
       </c>
-      <c r="C165">
+      <c r="C169">
+        <v>250</v>
+      </c>
+      <c r="D169">
         <v>1500</v>
       </c>
-      <c r="D165">
-        <v>1000</v>
-      </c>
-      <c r="E165">
-        <v>100</v>
-      </c>
-      <c r="F165">
-        <v>100000</v>
-      </c>
-      <c r="G165">
-        <v>54.444255477048188</v>
-      </c>
-      <c r="H165">
-        <v>5.3724000000000008E-2</v>
-      </c>
-      <c r="I165">
-        <v>9.1335245686139578E-10</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
-        <v>170</v>
-      </c>
-      <c r="B166">
+      <c r="E169">
+        <v>100</v>
+      </c>
+      <c r="F169">
+        <v>100000</v>
+      </c>
+      <c r="G169">
+        <v>48.9889231358995</v>
+      </c>
+      <c r="H169">
+        <v>0.02442</v>
+      </c>
+      <c r="I169">
+        <v>4.152526380820318E-10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170">
         <v>-0.9</v>
       </c>
-      <c r="C166">
-        <v>1750</v>
-      </c>
-      <c r="D166">
-        <v>1000</v>
-      </c>
-      <c r="E166">
-        <v>100</v>
-      </c>
-      <c r="F166">
-        <v>100000</v>
-      </c>
-      <c r="G166">
-        <v>36.269253943485722</v>
-      </c>
-      <c r="H166">
-        <v>2.9304E-2</v>
-      </c>
-      <c r="I166">
-        <v>4.9856197086816904E-10</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>171</v>
-      </c>
-      <c r="B167">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C167">
-        <v>1100</v>
-      </c>
-      <c r="D167">
-        <v>1000</v>
-      </c>
-      <c r="E167">
-        <v>100</v>
-      </c>
-      <c r="F167">
-        <v>100000</v>
-      </c>
-      <c r="G167">
-        <v>76.455176394334089</v>
-      </c>
-      <c r="H167">
-        <v>10.812732</v>
-      </c>
-      <c r="I167">
-        <v>1.8366044810537159E-7</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>172</v>
-      </c>
-      <c r="B168">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C168">
-        <v>1250</v>
-      </c>
-      <c r="D168">
-        <v>1000</v>
-      </c>
-      <c r="E168">
-        <v>100</v>
-      </c>
-      <c r="F168">
-        <v>100000</v>
-      </c>
-      <c r="G168">
-        <v>73.510022048059</v>
-      </c>
-      <c r="H168">
-        <v>14.124972</v>
-      </c>
-      <c r="I168">
-        <v>2.3994955065221879E-7</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>173</v>
-      </c>
-      <c r="B169">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C169">
+      <c r="C170">
+        <v>500</v>
+      </c>
+      <c r="D170">
         <v>1500</v>
       </c>
-      <c r="D169">
-        <v>1000</v>
-      </c>
-      <c r="E169">
-        <v>100</v>
-      </c>
-      <c r="F169">
-        <v>100000</v>
-      </c>
-      <c r="G169">
-        <v>66.653514082311787</v>
-      </c>
-      <c r="H169">
-        <v>18.334980000000002</v>
-      </c>
-      <c r="I169">
-        <v>3.1155462760571708E-7</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>174</v>
-      </c>
-      <c r="B170">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C170">
-        <v>1750</v>
-      </c>
-      <c r="D170">
-        <v>1000</v>
-      </c>
       <c r="E170">
         <v>100</v>
       </c>
@@ -6020,24 +6151,24 @@
         <v>100000</v>
       </c>
       <c r="G170">
-        <v>68.597893232805504</v>
+        <v>42.15397801682138</v>
       </c>
       <c r="H170">
-        <v>9.8883240000000008</v>
+        <v>0.031524</v>
       </c>
       <c r="I170">
-        <v>1.6801266390402811E-7</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.362029747455453E-10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B171">
         <v>-0.9</v>
       </c>
       <c r="C171">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D171">
         <v>1500</v>
@@ -6049,24 +6180,24 @@
         <v>100000</v>
       </c>
       <c r="G171">
-        <v>43.003393963551517</v>
+        <v>44.01705982940171</v>
       </c>
       <c r="H171">
-        <v>2.5752000000000001E-2</v>
+        <v>0.030192</v>
       </c>
       <c r="I171">
-        <v>4.3800977718827819E-10</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.135074559178064E-10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B172">
         <v>-0.9</v>
       </c>
       <c r="C172">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D172">
         <v>1500</v>
@@ -6078,24 +6209,24 @@
         <v>100000</v>
       </c>
       <c r="G172">
-        <v>48.988923135899498</v>
+        <v>52.01082595834881</v>
       </c>
       <c r="H172">
-        <v>2.4420000000000001E-2</v>
+        <v>0.031524</v>
       </c>
       <c r="I172">
-        <v>4.1525263808203178E-10</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.359873037707695E-10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B173">
         <v>-0.9</v>
       </c>
       <c r="C173">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D173">
         <v>1500</v>
@@ -6107,24 +6238,24 @@
         <v>100000</v>
       </c>
       <c r="G173">
-        <v>42.153978016821377</v>
+        <v>50.69164972968304</v>
       </c>
       <c r="H173">
-        <v>3.1524000000000003E-2</v>
+        <v>0.027972</v>
       </c>
       <c r="I173">
-        <v>5.3620297474554527E-10</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.756199709264007E-10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B174">
         <v>-0.9</v>
       </c>
       <c r="C174">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="D174">
         <v>1500</v>
@@ -6136,24 +6267,24 @@
         <v>100000</v>
       </c>
       <c r="G174">
-        <v>44.01705982940171</v>
+        <v>50.44743711681949</v>
       </c>
       <c r="H174">
-        <v>3.0192E-2</v>
+        <v>0.040404</v>
       </c>
       <c r="I174">
-        <v>5.1350745591780637E-10</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.870134713690796E-10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B175">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C175">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="D175">
         <v>1500</v>
@@ -6165,24 +6296,24 @@
         <v>100000</v>
       </c>
       <c r="G175">
-        <v>52.010825958348811</v>
+        <v>43.577794321377</v>
       </c>
       <c r="H175">
-        <v>3.1524000000000003E-2</v>
+        <v>0.038628</v>
       </c>
       <c r="I175">
-        <v>5.3598730377076951E-10</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.569992607127904E-10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B176">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C176">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="D176">
         <v>1500</v>
@@ -6194,24 +6325,24 @@
         <v>100000</v>
       </c>
       <c r="G176">
-        <v>50.691649729683043</v>
+        <v>45.61302951848488</v>
       </c>
       <c r="H176">
-        <v>2.7972E-2</v>
+        <v>0.03108</v>
       </c>
       <c r="I176">
-        <v>4.7561997092640075E-10</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.285761815244583E-10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B177">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C177">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="D177">
         <v>1500</v>
@@ -6223,24 +6354,24 @@
         <v>100000</v>
       </c>
       <c r="G177">
-        <v>50.447437116819493</v>
+        <v>74.69358085264865</v>
       </c>
       <c r="H177">
-        <v>4.0404000000000002E-2</v>
+        <v>0.096792</v>
       </c>
       <c r="I177">
-        <v>6.870134713690796E-10</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.644185648784016E-09</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B178">
         <v>-1</v>
       </c>
       <c r="C178">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D178">
         <v>1500</v>
@@ -6252,24 +6383,24 @@
         <v>100000</v>
       </c>
       <c r="G178">
-        <v>43.577794321376999</v>
+        <v>85.52396168691058</v>
       </c>
       <c r="H178">
-        <v>3.8628000000000003E-2</v>
+        <v>0.680208</v>
       </c>
       <c r="I178">
-        <v>6.5699926071279044E-10</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.154945285547047E-08</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B179">
         <v>-1</v>
       </c>
       <c r="C179">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D179">
         <v>1500</v>
@@ -6281,24 +6412,24 @@
         <v>100000</v>
       </c>
       <c r="G179">
-        <v>45.613029518484879</v>
+        <v>87.63767287098989</v>
       </c>
       <c r="H179">
-        <v>3.108E-2</v>
+        <v>0.9768</v>
       </c>
       <c r="I179">
-        <v>5.2857618152445829E-10</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.65839477150549E-08</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B180">
         <v>-1</v>
       </c>
       <c r="C180">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D180">
         <v>1500</v>
@@ -6310,24 +6441,24 @@
         <v>100000</v>
       </c>
       <c r="G180">
-        <v>74.693580852648651</v>
+        <v>88.75432454940012</v>
       </c>
       <c r="H180">
-        <v>9.6792000000000003E-2</v>
+        <v>1.41858</v>
       </c>
       <c r="I180">
-        <v>1.6441856487840159E-9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.408331918647932E-08</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B181">
         <v>-1</v>
       </c>
       <c r="C181">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="D181">
         <v>1500</v>
@@ -6339,24 +6470,24 @@
         <v>100000</v>
       </c>
       <c r="G181">
-        <v>85.523961686910582</v>
+        <v>87.95683835500725</v>
       </c>
       <c r="H181">
-        <v>0.68020800000000003</v>
+        <v>1.5873</v>
       </c>
       <c r="I181">
-        <v>1.1549452855470471E-8</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.694856457163021E-08</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B182">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C182">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="D182">
         <v>1500</v>
@@ -6368,24 +6499,24 @@
         <v>100000</v>
       </c>
       <c r="G182">
-        <v>87.637672870989888</v>
+        <v>47.51726538906836</v>
       </c>
       <c r="H182">
-        <v>0.9768</v>
+        <v>0.037296</v>
       </c>
       <c r="I182">
-        <v>1.6583947715054899E-8</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.342421216065442E-10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B183">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C183">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="D183">
         <v>1500</v>
@@ -6397,24 +6528,24 @@
         <v>100000</v>
       </c>
       <c r="G183">
-        <v>88.754324549400124</v>
+        <v>85.16590828660399</v>
       </c>
       <c r="H183">
-        <v>1.41858</v>
+        <v>0.45954</v>
       </c>
       <c r="I183">
-        <v>2.408331918647932E-8</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.802779452748202E-09</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B184">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C184">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="D184">
         <v>1500</v>
@@ -6426,24 +6557,24 @@
         <v>100000</v>
       </c>
       <c r="G184">
-        <v>87.95683835500725</v>
+        <v>85.67300235252691</v>
       </c>
       <c r="H184">
-        <v>1.5872999999999999</v>
+        <v>1.452324</v>
       </c>
       <c r="I184">
-        <v>2.6948564571630209E-8</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.465928906471075E-08</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B185">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C185">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D185">
         <v>1500</v>
@@ -6455,24 +6586,24 @@
         <v>100000</v>
       </c>
       <c r="G185">
-        <v>47.517265389068363</v>
+        <v>83.81442428284544</v>
       </c>
       <c r="H185">
-        <v>3.7296000000000003E-2</v>
+        <v>2.276388</v>
       </c>
       <c r="I185">
-        <v>6.342421216065442E-10</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.86541580778151E-08</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B186">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C186">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D186">
         <v>1500</v>
@@ -6484,24 +6615,24 @@
         <v>100000</v>
       </c>
       <c r="G186">
-        <v>85.165908286603994</v>
+        <v>84.70628549644064</v>
       </c>
       <c r="H186">
-        <v>0.45954</v>
+        <v>2.543232000000001</v>
       </c>
       <c r="I186">
-        <v>7.8027794527482022E-9</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.318372738901967E-08</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B187">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C187">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D187">
         <v>1500</v>
@@ -6513,24 +6644,24 @@
         <v>100000</v>
       </c>
       <c r="G187">
-        <v>85.673002352526908</v>
+        <v>75.5138672310635</v>
       </c>
       <c r="H187">
-        <v>1.4523239999999999</v>
+        <v>10.454868</v>
       </c>
       <c r="I187">
-        <v>2.4659289064710748E-8</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.77588737610347E-07</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B188">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="C188">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="D188">
         <v>1500</v>
@@ -6542,24 +6673,24 @@
         <v>100000</v>
       </c>
       <c r="G188">
-        <v>83.814424282845437</v>
+        <v>73.40288926426662</v>
       </c>
       <c r="H188">
-        <v>2.2763879999999999</v>
+        <v>14.804736</v>
       </c>
       <c r="I188">
-        <v>3.8654158077815098E-8</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.514982165653825E-07</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B189">
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="C189">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="D189">
         <v>1500</v>
@@ -6571,24 +6702,24 @@
         <v>100000</v>
       </c>
       <c r="G189">
-        <v>84.706285496440643</v>
+        <v>74.27880843320926</v>
       </c>
       <c r="H189">
-        <v>2.543232000000001</v>
+        <v>0.5003880000000001</v>
       </c>
       <c r="I189">
-        <v>4.3183727389019668E-8</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.500131009592692E-09</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B190">
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="C190">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="D190">
         <v>1500</v>
@@ -6600,24 +6731,24 @@
         <v>100000</v>
       </c>
       <c r="G190">
-        <v>75.5138672310635</v>
+        <v>76.7580571699902</v>
       </c>
       <c r="H190">
-        <v>10.454867999999999</v>
+        <v>2.146296</v>
       </c>
       <c r="I190">
-        <v>1.77588737610347E-7</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.645561714724191E-08</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B191">
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="C191">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="D191">
         <v>1500</v>
@@ -6629,24 +6760,24 @@
         <v>100000</v>
       </c>
       <c r="G191">
-        <v>73.402889264266619</v>
+        <v>78.77835618311246</v>
       </c>
       <c r="H191">
-        <v>14.804736</v>
+        <v>2.455764</v>
       </c>
       <c r="I191">
-        <v>2.5149821656538251E-7</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.170860852812281E-08</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B192">
         <v>-1.2</v>
       </c>
       <c r="C192">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D192">
         <v>1500</v>
@@ -6658,24 +6789,24 @@
         <v>100000</v>
       </c>
       <c r="G192">
-        <v>74.278808433209264</v>
+        <v>79.18639974596287</v>
       </c>
       <c r="H192">
-        <v>0.50038800000000005</v>
+        <v>3.937836</v>
       </c>
       <c r="I192">
-        <v>8.5001310095926916E-9</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.687895435892488E-08</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B193">
         <v>-1.2</v>
       </c>
       <c r="C193">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D193">
         <v>1500</v>
@@ -6687,143 +6818,143 @@
         <v>100000</v>
       </c>
       <c r="G193">
-        <v>76.758057169990195</v>
+        <v>66.77953872335911</v>
       </c>
       <c r="H193">
-        <v>2.146296</v>
+        <v>21.6894</v>
       </c>
       <c r="I193">
-        <v>3.6455617147241907E-8</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.685522542361557E-07</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B194">
         <v>-1.2</v>
       </c>
       <c r="C194">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D194">
         <v>1500</v>
       </c>
       <c r="E194">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F194">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G194">
-        <v>78.778356183112464</v>
+        <v>63.17215282092562</v>
       </c>
       <c r="H194">
-        <v>2.4557639999999998</v>
+        <v>15.115092</v>
       </c>
       <c r="I194">
-        <v>4.1708608528122813E-8</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.568775937049936E-07</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B195">
         <v>-1.2</v>
       </c>
       <c r="C195">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="D195">
         <v>1500</v>
       </c>
       <c r="E195">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F195">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G195">
-        <v>79.186399745962873</v>
+        <v>63.08246180136499</v>
       </c>
       <c r="H195">
-        <v>3.9378359999999999</v>
+        <v>15.893424</v>
       </c>
       <c r="I195">
-        <v>6.6878954358924882E-8</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.701061593533595E-07</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B196">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="C196">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D196">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E196">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F196">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G196">
-        <v>66.77953872335911</v>
+        <v>84.735769631919</v>
       </c>
       <c r="H196">
-        <v>21.689399999999999</v>
+        <v>0.4932840000000001</v>
       </c>
       <c r="I196">
-        <v>3.6855225423615572E-7</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.375883988029037E-09</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B197">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="C197">
         <v>1500</v>
       </c>
       <c r="D197">
+        <v>1000</v>
+      </c>
+      <c r="E197">
+        <v>25</v>
+      </c>
+      <c r="F197">
+        <v>25000</v>
+      </c>
+      <c r="G197">
+        <v>85.00018646250633</v>
+      </c>
+      <c r="H197">
+        <v>0.7663440000000001</v>
+      </c>
+      <c r="I197">
+        <v>1.301225921446809E-08</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198">
+        <v>-1</v>
+      </c>
+      <c r="C198">
         <v>1500</v>
       </c>
-      <c r="E197">
-        <v>50</v>
-      </c>
-      <c r="F197">
-        <v>50000</v>
-      </c>
-      <c r="G197">
-        <v>63.172152820925618</v>
-      </c>
-      <c r="H197">
-        <v>15.115092000000001</v>
-      </c>
-      <c r="I197">
-        <v>2.5687759370499358E-7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>202</v>
-      </c>
-      <c r="B198">
-        <v>-1.2</v>
-      </c>
-      <c r="C198">
-        <v>1750</v>
-      </c>
       <c r="D198">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E198">
         <v>50</v>
@@ -6832,85 +6963,85 @@
         <v>50000</v>
       </c>
       <c r="G198">
-        <v>63.082461801364992</v>
+        <v>87.70865004435213</v>
       </c>
       <c r="H198">
-        <v>15.893424</v>
+        <v>1.0767</v>
       </c>
       <c r="I198">
-        <v>2.7010615935335951E-7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.827998040942384E-08</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B199">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C199">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E199">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F199">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="G199">
-        <v>80.883542598691037</v>
+        <v>86.3886819838646</v>
       </c>
       <c r="H199">
-        <v>6.9046440000000002</v>
+        <v>1.106448</v>
       </c>
       <c r="I199">
-        <v>1.17258166397131E-7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.878604593295609E-08</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B200">
         <v>-1</v>
       </c>
       <c r="C200">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E200">
-        <v>100</v>
+        <v>76.5</v>
       </c>
       <c r="F200">
-        <v>100000</v>
+        <v>76500</v>
       </c>
       <c r="G200">
-        <v>63.570068106098077</v>
+        <v>85.80388605320117</v>
       </c>
       <c r="H200">
-        <v>15.336648</v>
+        <v>1.594404</v>
       </c>
       <c r="I200">
-        <v>2.6063865801025888E-7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.707154837748447E-08</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B201">
-        <v>-1.1000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="C201">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E201">
         <v>100</v>
@@ -6919,105 +7050,105 @@
         <v>100000</v>
       </c>
       <c r="G201">
-        <v>53.661605043601277</v>
+        <v>88.45456174559649</v>
       </c>
       <c r="H201">
-        <v>24.211320000000001</v>
+        <v>1.972248</v>
       </c>
       <c r="I201">
-        <v>4.116256197063687E-7</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.348338355353263E-08</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B202">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="C202">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E202">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F202">
-        <v>100000</v>
+        <v>114000</v>
       </c>
       <c r="G202">
-        <v>50.564617695512908</v>
+        <v>87.90288174879107</v>
       </c>
       <c r="H202">
-        <v>28.972776</v>
+        <v>1.81596</v>
       </c>
       <c r="I202">
-        <v>4.9263915037108787E-7</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.083073326425532E-08</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B203">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="C203">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E203">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="F203">
-        <v>100000</v>
+        <v>900000</v>
       </c>
       <c r="G203">
-        <v>50.261902015015593</v>
+        <v>90.44991634388766</v>
       </c>
       <c r="H203">
-        <v>31.416108000000001</v>
+        <v>9.482063999999999</v>
       </c>
       <c r="I203">
-        <v>5.3419099177566485E-7</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.609664582307931E-07</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B204">
-        <v>-1.4</v>
+        <v>-1</v>
       </c>
       <c r="C204">
-        <v>100000</v>
+        <v>1500</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E204">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F204">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="G204">
-        <v>50.264041402040419</v>
+        <v>88.62570624887859</v>
       </c>
       <c r="H204">
-        <v>33.961560000000013</v>
+        <v>2.620932</v>
       </c>
       <c r="I204">
-        <v>5.7747311776316999E-7</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.449595561119397E-08</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B205">
         <v>-1</v>
@@ -7029,24 +7160,24 @@
         <v>1000</v>
       </c>
       <c r="E205">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F205">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
       <c r="G205">
-        <v>84.735769631918998</v>
+        <v>89.95287426741695</v>
       </c>
       <c r="H205">
-        <v>0.49328400000000011</v>
+        <v>11.203896</v>
       </c>
       <c r="I205">
-        <v>8.3758839880290367E-9</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.901999373908826E-07</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B206">
         <v>-1</v>
@@ -7055,27 +7186,27 @@
         <v>1500</v>
       </c>
       <c r="D206">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E206">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F206">
-        <v>25000</v>
+        <v>100000</v>
       </c>
       <c r="G206">
-        <v>85.000186462506335</v>
+        <v>69.0618086758801</v>
       </c>
       <c r="H206">
-        <v>0.76634400000000014</v>
+        <v>11.352192</v>
       </c>
       <c r="I206">
-        <v>1.301225921446809E-8</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.928816185338716E-07</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B207">
         <v>-1</v>
@@ -7084,27 +7215,27 @@
         <v>1500</v>
       </c>
       <c r="D207">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E207">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F207">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G207">
-        <v>87.708650044352126</v>
+        <v>73.47307864506178</v>
       </c>
       <c r="H207">
-        <v>1.0767</v>
+        <v>10.275936</v>
       </c>
       <c r="I207">
-        <v>1.827998040942384E-8</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.745638815825482E-07</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B208">
         <v>-1</v>
@@ -7113,27 +7244,27 @@
         <v>1500</v>
       </c>
       <c r="D208">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="E208">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F208">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="G208">
-        <v>86.388681983864601</v>
+        <v>77.24991015234681</v>
       </c>
       <c r="H208">
-        <v>1.1064480000000001</v>
+        <v>9.094008000000002</v>
       </c>
       <c r="I208">
-        <v>1.878604593295609E-8</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.544619320345561E-07</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B209">
         <v>-1</v>
@@ -7142,36 +7273,36 @@
         <v>1500</v>
       </c>
       <c r="D209">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E209">
-        <v>76.5</v>
+        <v>100</v>
       </c>
       <c r="F209">
-        <v>76500</v>
+        <v>100000</v>
       </c>
       <c r="G209">
-        <v>85.803886053201168</v>
+        <v>80.76208414134435</v>
       </c>
       <c r="H209">
-        <v>1.5944039999999999</v>
+        <v>6.444216000000001</v>
       </c>
       <c r="I209">
-        <v>2.7071548377484469E-8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.094394863450163E-07</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B210">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="C210">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D210">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E210">
         <v>100</v>
@@ -7180,201 +7311,201 @@
         <v>100000</v>
       </c>
       <c r="G210">
-        <v>88.454561745596493</v>
+        <v>82.19265302587954</v>
       </c>
       <c r="H210">
-        <v>1.972248</v>
+        <v>5.346204</v>
       </c>
       <c r="I210">
-        <v>3.3483383553532632E-8</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.078710378243323E-08</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B211">
         <v>-1</v>
       </c>
       <c r="C211">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D211">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E211">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F211">
-        <v>114000</v>
+        <v>100000</v>
       </c>
       <c r="G211">
-        <v>87.902881748791074</v>
+        <v>65.2086209736138</v>
       </c>
       <c r="H211">
-        <v>1.81596</v>
+        <v>13.114428</v>
       </c>
       <c r="I211">
-        <v>3.0830733264255318E-8</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.228582472390504E-07</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B212">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C212">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D212">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E212">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="F212">
-        <v>900000</v>
+        <v>100000</v>
       </c>
       <c r="G212">
-        <v>90.449916343887665</v>
+        <v>53.54289881581275</v>
       </c>
       <c r="H212">
-        <v>9.4820639999999994</v>
+        <v>20.906184</v>
       </c>
       <c r="I212">
-        <v>1.6096645823079311E-7</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.554354998668971E-07</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B213">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="C213">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D213">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E213">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F213">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="G213">
-        <v>88.625706248878586</v>
+        <v>50.12435911516626</v>
       </c>
       <c r="H213">
-        <v>2.6209319999999998</v>
+        <v>26.379372</v>
       </c>
       <c r="I213">
-        <v>4.4495955611193973E-8</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.485502146720162E-07</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B214">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="C214">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D214">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E214">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F214">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="G214">
-        <v>89.952874267416945</v>
+        <v>49.60346950438729</v>
       </c>
       <c r="H214">
-        <v>11.203896</v>
+        <v>28.493256</v>
       </c>
       <c r="I214">
-        <v>1.901999373908826E-7</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.845046265951931E-07</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B215">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="C215">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D215">
         <v>10</v>
       </c>
       <c r="E215">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F215">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G215">
-        <v>69.061808675880101</v>
+        <v>49.42936369321656</v>
       </c>
       <c r="H215">
-        <v>11.352192000000001</v>
+        <v>16.48572</v>
       </c>
       <c r="I215">
-        <v>1.9288161853387159E-7</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.803282420869683E-07</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B216">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="C216">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D216">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E216">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F216">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G216">
-        <v>73.473078645061776</v>
+        <v>49.29938443055411</v>
       </c>
       <c r="H216">
-        <v>10.275936</v>
+        <v>18.580068</v>
       </c>
       <c r="I216">
-        <v>1.745638815825482E-7</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.159428541193396E-07</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B217">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="C217">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="D217">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="E217">
         <v>100</v>
@@ -7383,27 +7514,27 @@
         <v>100000</v>
       </c>
       <c r="G217">
-        <v>77.249910152346814</v>
+        <v>79.93462494466955</v>
       </c>
       <c r="H217">
-        <v>9.0940080000000023</v>
+        <v>5.614380000000001</v>
       </c>
       <c r="I217">
-        <v>1.544619320345561E-7</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.534993649022959E-08</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B218">
         <v>-1</v>
       </c>
       <c r="C218">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="D218">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E218">
         <v>100</v>
@@ -7412,393 +7543,1988 @@
         <v>100000</v>
       </c>
       <c r="G218">
-        <v>80.762084141344346</v>
+        <v>65.42383543145775</v>
       </c>
       <c r="H218">
-        <v>6.4442160000000008</v>
+        <v>13.326216</v>
       </c>
       <c r="I218">
-        <v>1.094394863450163E-7</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.264552501203015E-07</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B219">
+        <v>-1.1</v>
+      </c>
+      <c r="C219">
+        <v>4000</v>
+      </c>
+      <c r="D219">
+        <v>10</v>
+      </c>
+      <c r="E219">
+        <v>100</v>
+      </c>
+      <c r="F219">
+        <v>100000</v>
+      </c>
+      <c r="G219">
+        <v>53.7665673331326</v>
+      </c>
+      <c r="H219">
+        <v>19.858344</v>
+      </c>
+      <c r="I219">
+        <v>3.376176163447789E-07</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220">
+        <v>-1.2</v>
+      </c>
+      <c r="C220">
+        <v>4000</v>
+      </c>
+      <c r="D220">
+        <v>10</v>
+      </c>
+      <c r="E220">
+        <v>100</v>
+      </c>
+      <c r="F220">
+        <v>100000</v>
+      </c>
+      <c r="G220">
+        <v>49.93622091028458</v>
+      </c>
+      <c r="H220">
+        <v>21.477612</v>
+      </c>
+      <c r="I220">
+        <v>3.652043513307705E-07</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221">
+        <v>-1.3</v>
+      </c>
+      <c r="C221">
+        <v>4000</v>
+      </c>
+      <c r="D221">
+        <v>10</v>
+      </c>
+      <c r="E221">
+        <v>100</v>
+      </c>
+      <c r="F221">
+        <v>100000</v>
+      </c>
+      <c r="G221">
+        <v>49.5944854703945</v>
+      </c>
+      <c r="H221">
+        <v>28.308108</v>
+      </c>
+      <c r="I221">
+        <v>4.813565120377985E-07</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222">
+        <v>-1.4</v>
+      </c>
+      <c r="C222">
+        <v>4000</v>
+      </c>
+      <c r="D222">
+        <v>10</v>
+      </c>
+      <c r="E222">
+        <v>50</v>
+      </c>
+      <c r="F222">
+        <v>50000</v>
+      </c>
+      <c r="G222">
+        <v>49.5203050429509</v>
+      </c>
+      <c r="H222">
+        <v>15.165264</v>
+      </c>
+      <c r="I222">
+        <v>2.578738459765401E-07</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223">
+        <v>-1.5</v>
+      </c>
+      <c r="C223">
+        <v>4000</v>
+      </c>
+      <c r="D223">
+        <v>10</v>
+      </c>
+      <c r="E223">
+        <v>50</v>
+      </c>
+      <c r="F223">
+        <v>50000</v>
+      </c>
+      <c r="G223">
+        <v>49.38506772557209</v>
+      </c>
+      <c r="H223">
+        <v>18.005088</v>
+      </c>
+      <c r="I223">
+        <v>3.061645952929475E-07</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224">
         <v>-0.9</v>
       </c>
-      <c r="C219">
-        <v>1952</v>
-      </c>
-      <c r="D219">
-        <v>1401</v>
-      </c>
-      <c r="E219">
-        <v>1007.232</v>
-      </c>
-      <c r="F219">
-        <v>1007232</v>
-      </c>
-      <c r="G219">
-        <v>88.47</v>
-      </c>
-      <c r="H219">
-        <v>0.92</v>
-      </c>
-      <c r="I219">
-        <v>1.5686400000000001E-8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>224</v>
-      </c>
-      <c r="B220">
-        <v>-1</v>
-      </c>
-      <c r="C220">
-        <v>1505</v>
-      </c>
-      <c r="D220">
-        <v>1273</v>
-      </c>
-      <c r="E220">
-        <v>1008.35</v>
-      </c>
-      <c r="F220">
-        <v>1008350</v>
-      </c>
-      <c r="G220">
-        <v>87.35</v>
-      </c>
-      <c r="H220">
-        <v>4.34</v>
-      </c>
-      <c r="I220">
-        <v>7.3754199999999997E-8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>225</v>
-      </c>
-      <c r="B221">
-        <v>-1</v>
-      </c>
-      <c r="C221">
-        <v>1491</v>
-      </c>
-      <c r="D221">
-        <v>1272</v>
-      </c>
-      <c r="E221">
-        <v>1255.422</v>
-      </c>
-      <c r="F221">
-        <v>1255422</v>
-      </c>
-      <c r="G221">
-        <v>88.94</v>
-      </c>
-      <c r="H221">
-        <v>4.71</v>
-      </c>
-      <c r="I221">
-        <v>7.9960499999999997E-8</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
-        <v>226</v>
-      </c>
-      <c r="B222">
-        <v>-0.9</v>
-      </c>
-      <c r="C222">
-        <v>3025</v>
-      </c>
-      <c r="D222">
-        <v>1361</v>
-      </c>
-      <c r="E222">
-        <v>974.05</v>
-      </c>
-      <c r="F222">
-        <v>974050</v>
-      </c>
-      <c r="G222">
-        <v>89.32</v>
-      </c>
-      <c r="H222">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="I222">
-        <v>1.89044E-8</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
-        <v>227</v>
-      </c>
-      <c r="B223">
-        <v>-0.9</v>
-      </c>
-      <c r="C223">
-        <v>2013</v>
-      </c>
-      <c r="D223">
-        <v>1418</v>
-      </c>
-      <c r="E223">
-        <v>515.32799999999997</v>
-      </c>
-      <c r="F223">
-        <v>515328</v>
-      </c>
-      <c r="G223">
-        <v>80.66</v>
-      </c>
-      <c r="H223">
-        <v>0.18</v>
-      </c>
-      <c r="I223">
-        <v>3.12923E-9</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>228</v>
-      </c>
-      <c r="B224">
-        <v>-1</v>
-      </c>
       <c r="C224">
-        <v>785</v>
+        <v>5</v>
       </c>
       <c r="D224">
-        <v>1086</v>
+        <v>250</v>
       </c>
       <c r="E224">
-        <v>993.02499999999998</v>
+        <v>100</v>
       </c>
       <c r="F224">
-        <v>993025</v>
+        <v>100000</v>
       </c>
       <c r="G224">
-        <v>88.26</v>
+        <v>43.29600964792143</v>
       </c>
       <c r="H224">
-        <v>2.48</v>
+        <v>0.023532</v>
       </c>
       <c r="I224">
-        <v>4.2129699999999998E-8</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.002455327538873E-10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B225">
         <v>-1</v>
       </c>
       <c r="C225">
-        <v>1482</v>
+        <v>5</v>
       </c>
       <c r="D225">
-        <v>1271</v>
+        <v>250</v>
       </c>
       <c r="E225">
-        <v>1447.914</v>
+        <v>100</v>
       </c>
       <c r="F225">
-        <v>1447914</v>
+        <v>100000</v>
       </c>
       <c r="G225">
-        <v>88.64</v>
+        <v>43.49967429013609</v>
       </c>
       <c r="H225">
-        <v>2.63</v>
+        <v>0.111</v>
       </c>
       <c r="I225">
-        <v>4.4624100000000002E-8</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.887934930466263E-09</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B226">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="C226">
-        <v>2777.4</v>
+        <v>5</v>
       </c>
       <c r="D226">
-        <v>1002.4</v>
+        <v>250</v>
       </c>
       <c r="E226">
-        <v>902.65499999999997</v>
+        <v>100</v>
       </c>
       <c r="F226">
-        <v>902655</v>
+        <v>100000</v>
       </c>
       <c r="G226">
-        <v>89.97</v>
+        <v>47.12052517238122</v>
       </c>
       <c r="H226">
-        <v>4.75</v>
+        <v>0.111888</v>
       </c>
       <c r="I226">
-        <v>8.0575200000000003E-8</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.902757174958886E-09</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B227">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="C227">
-        <v>2839.6</v>
+        <v>5</v>
       </c>
       <c r="D227">
-        <v>885</v>
+        <v>250</v>
       </c>
       <c r="E227">
-        <v>445.81720000000001</v>
+        <v>100</v>
       </c>
       <c r="F227">
-        <v>445817.2</v>
+        <v>100000</v>
       </c>
       <c r="G227">
-        <v>74.81</v>
+        <v>46.69643776921086</v>
       </c>
       <c r="H227">
-        <v>52.98</v>
+        <v>0.09013200000000002</v>
       </c>
       <c r="I227">
-        <v>8.9988599999999999E-7</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.532803144114571E-09</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B228">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="C228">
-        <v>3044.4</v>
+        <v>5</v>
       </c>
       <c r="D228">
-        <v>788.783861</v>
+        <v>250</v>
       </c>
       <c r="E228">
-        <v>106.554</v>
+        <v>100</v>
       </c>
       <c r="F228">
-        <v>106554</v>
+        <v>100000</v>
       </c>
       <c r="G228">
-        <v>73.989999999999995</v>
+        <v>45.02091894065987</v>
       </c>
       <c r="H228">
-        <v>10.58</v>
+        <v>0.036408</v>
       </c>
       <c r="I228">
-        <v>1.7971199999999999E-7</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.192042061391458E-10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B229">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="C229">
-        <v>2948.8</v>
+        <v>5</v>
       </c>
       <c r="D229">
-        <v>894.8</v>
+        <v>250</v>
       </c>
       <c r="E229">
-        <v>215.26240000000001</v>
+        <v>100</v>
       </c>
       <c r="F229">
-        <v>215262.4</v>
+        <v>100000</v>
       </c>
       <c r="G229">
-        <v>88.01</v>
+        <v>50.69164972968304</v>
       </c>
       <c r="H229">
-        <v>1.69</v>
+        <v>0.027972</v>
       </c>
       <c r="I229">
-        <v>2.87199E-8</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.756199709264007E-10</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B230">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="C230">
-        <v>2978.6</v>
+        <v>5</v>
       </c>
       <c r="D230">
-        <v>826.414356</v>
+        <v>250</v>
       </c>
       <c r="E230">
-        <v>268.07400000000001</v>
+        <v>100</v>
       </c>
       <c r="F230">
-        <v>268074</v>
+        <v>100000</v>
       </c>
       <c r="G230">
-        <v>72.86</v>
+        <v>44.79701903694631</v>
       </c>
       <c r="H230">
-        <v>28.7</v>
+        <v>0.021756</v>
       </c>
       <c r="I230">
-        <v>4.8755999999999995E-7</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.700156511228223E-10</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B231">
         <v>-0.9</v>
       </c>
       <c r="C231">
-        <v>2859.6</v>
+        <v>10</v>
       </c>
       <c r="D231">
-        <v>912</v>
+        <v>250</v>
       </c>
       <c r="E231">
-        <v>1075.2095999999999</v>
+        <v>100</v>
       </c>
       <c r="F231">
-        <v>1075209.6000000001</v>
+        <v>100000</v>
       </c>
       <c r="G231">
-        <v>86.27</v>
+        <v>48.4985711906168</v>
       </c>
       <c r="H231">
-        <v>1.1100000000000001</v>
+        <v>0.174492</v>
       </c>
       <c r="I231">
-        <v>1.8838899999999999E-8</v>
+        <v>2.967228229836353E-09</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232">
+        <v>-1</v>
+      </c>
+      <c r="C232">
+        <v>10</v>
+      </c>
+      <c r="D232">
+        <v>250</v>
+      </c>
+      <c r="E232">
+        <v>100</v>
+      </c>
+      <c r="F232">
+        <v>100000</v>
+      </c>
+      <c r="G232">
+        <v>35.80358271130459</v>
+      </c>
+      <c r="H232">
+        <v>0.017316</v>
+      </c>
+      <c r="I232">
+        <v>2.946104028110551E-10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233">
+        <v>-1.1</v>
+      </c>
+      <c r="C233">
+        <v>10</v>
+      </c>
+      <c r="D233">
+        <v>250</v>
+      </c>
+      <c r="E233">
+        <v>100</v>
+      </c>
+      <c r="F233">
+        <v>100000</v>
+      </c>
+      <c r="G233">
+        <v>47.26669112580649</v>
+      </c>
+      <c r="H233">
+        <v>0.04218</v>
+      </c>
+      <c r="I233">
+        <v>7.173049732786519E-10</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234">
+        <v>-1.2</v>
+      </c>
+      <c r="C234">
+        <v>10</v>
+      </c>
+      <c r="D234">
+        <v>250</v>
+      </c>
+      <c r="E234">
+        <v>100</v>
+      </c>
+      <c r="F234">
+        <v>100000</v>
+      </c>
+      <c r="G234">
+        <v>45.80031828227904</v>
+      </c>
+      <c r="H234">
+        <v>0.027084</v>
+      </c>
+      <c r="I234">
+        <v>4.606128655982562E-10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235">
+        <v>-1.3</v>
+      </c>
+      <c r="C235">
+        <v>10</v>
+      </c>
+      <c r="D235">
+        <v>250</v>
+      </c>
+      <c r="E235">
+        <v>100</v>
+      </c>
+      <c r="F235">
+        <v>100000</v>
+      </c>
+      <c r="G235">
+        <v>42.60850934228606</v>
+      </c>
+      <c r="H235">
+        <v>0.042624</v>
+      </c>
+      <c r="I235">
+        <v>7.249933867782463E-10</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236">
+        <v>-1.4</v>
+      </c>
+      <c r="C236">
+        <v>10</v>
+      </c>
+      <c r="D236">
+        <v>250</v>
+      </c>
+      <c r="E236">
+        <v>100</v>
+      </c>
+      <c r="F236">
+        <v>100000</v>
+      </c>
+      <c r="G236">
+        <v>79.98679065281432</v>
+      </c>
+      <c r="H236">
+        <v>0.5119320000000001</v>
+      </c>
+      <c r="I236">
+        <v>8.694206644263202E-09</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237">
+        <v>-1.5</v>
+      </c>
+      <c r="C237">
+        <v>10</v>
+      </c>
+      <c r="D237">
+        <v>250</v>
+      </c>
+      <c r="E237">
+        <v>100</v>
+      </c>
+      <c r="F237">
+        <v>100000</v>
+      </c>
+      <c r="G237">
+        <v>77.63820777215317</v>
+      </c>
+      <c r="H237">
+        <v>0.573648</v>
+      </c>
+      <c r="I237">
+        <v>9.743270062002226E-09</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238">
+        <v>-0.9</v>
+      </c>
+      <c r="C238">
+        <v>2000</v>
+      </c>
+      <c r="D238">
+        <v>250</v>
+      </c>
+      <c r="E238">
+        <v>100</v>
+      </c>
+      <c r="F238">
+        <v>100000</v>
+      </c>
+      <c r="G238">
+        <v>49.1346447137007</v>
+      </c>
+      <c r="H238">
+        <v>0.116328</v>
+      </c>
+      <c r="I238">
+        <v>1.978100802992146E-09</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239">
+        <v>-1</v>
+      </c>
+      <c r="C239">
+        <v>2000</v>
+      </c>
+      <c r="D239">
+        <v>250</v>
+      </c>
+      <c r="E239">
+        <v>100</v>
+      </c>
+      <c r="F239">
+        <v>100000</v>
+      </c>
+      <c r="G239">
+        <v>74.11336563118816</v>
+      </c>
+      <c r="H239">
+        <v>8.746356</v>
+      </c>
+      <c r="I239">
+        <v>1.485760516106842E-07</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240">
+        <v>-1.1</v>
+      </c>
+      <c r="C240">
+        <v>2000</v>
+      </c>
+      <c r="D240">
+        <v>250</v>
+      </c>
+      <c r="E240">
+        <v>100</v>
+      </c>
+      <c r="F240">
+        <v>100000</v>
+      </c>
+      <c r="G240">
+        <v>57.32939554837161</v>
+      </c>
+      <c r="H240">
+        <v>19.471176</v>
+      </c>
+      <c r="I240">
+        <v>3.309871408667845E-07</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241">
+        <v>-1.2</v>
+      </c>
+      <c r="C241">
+        <v>2000</v>
+      </c>
+      <c r="D241">
+        <v>250</v>
+      </c>
+      <c r="E241">
+        <v>100</v>
+      </c>
+      <c r="F241">
+        <v>100000</v>
+      </c>
+      <c r="G241">
+        <v>50.94663232325509</v>
+      </c>
+      <c r="H241">
+        <v>25.89186</v>
+      </c>
+      <c r="I241">
+        <v>4.4024587311109E-07</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242">
+        <v>-1.3</v>
+      </c>
+      <c r="C242">
+        <v>2000</v>
+      </c>
+      <c r="D242">
+        <v>250</v>
+      </c>
+      <c r="E242">
+        <v>50</v>
+      </c>
+      <c r="F242">
+        <v>50000</v>
+      </c>
+      <c r="G242">
+        <v>49.53572513595276</v>
+      </c>
+      <c r="H242">
+        <v>15.933384</v>
+      </c>
+      <c r="I242">
+        <v>2.709349752068878E-07</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243">
+        <v>-1.4</v>
+      </c>
+      <c r="C243">
+        <v>2000</v>
+      </c>
+      <c r="D243">
+        <v>250</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243">
+        <v>50000</v>
+      </c>
+      <c r="G243">
+        <v>49.44391282130697</v>
+      </c>
+      <c r="H243">
+        <v>17.551764</v>
+      </c>
+      <c r="I243">
+        <v>2.984554042056939E-07</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244">
+        <v>-1.5</v>
+      </c>
+      <c r="C244">
+        <v>2000</v>
+      </c>
+      <c r="D244">
+        <v>250</v>
+      </c>
+      <c r="E244">
+        <v>25</v>
+      </c>
+      <c r="F244">
+        <v>25000</v>
+      </c>
+      <c r="G244">
+        <v>49.54454106049251</v>
+      </c>
+      <c r="H244">
+        <v>11.054712</v>
+      </c>
+      <c r="I244">
+        <v>1.879768317930336E-07</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245">
+        <v>-0.9</v>
+      </c>
+      <c r="C245">
+        <v>4000</v>
+      </c>
+      <c r="D245">
+        <v>250</v>
+      </c>
+      <c r="E245">
+        <v>100</v>
+      </c>
+      <c r="F245">
+        <v>100000</v>
+      </c>
+      <c r="G245">
+        <v>49.89797653460296</v>
+      </c>
+      <c r="H245">
+        <v>0.023976</v>
+      </c>
+      <c r="I245">
+        <v>4.076874651394523E-10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246">
+        <v>-1</v>
+      </c>
+      <c r="C246">
+        <v>4000</v>
+      </c>
+      <c r="D246">
+        <v>250</v>
+      </c>
+      <c r="E246">
+        <v>100</v>
+      </c>
+      <c r="F246">
+        <v>100000</v>
+      </c>
+      <c r="G246">
+        <v>68.54893178923966</v>
+      </c>
+      <c r="H246">
+        <v>10.839816</v>
+      </c>
+      <c r="I246">
+        <v>1.841798467166659E-07</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247">
+        <v>-1.1</v>
+      </c>
+      <c r="C247">
+        <v>4000</v>
+      </c>
+      <c r="D247">
+        <v>250</v>
+      </c>
+      <c r="E247">
+        <v>100</v>
+      </c>
+      <c r="F247">
+        <v>100000</v>
+      </c>
+      <c r="G247">
+        <v>55.24845772113844</v>
+      </c>
+      <c r="H247">
+        <v>20.310336</v>
+      </c>
+      <c r="I247">
+        <v>3.452811891696E-07</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248">
+        <v>-1.2</v>
+      </c>
+      <c r="C248">
+        <v>4000</v>
+      </c>
+      <c r="D248">
+        <v>250</v>
+      </c>
+      <c r="E248">
+        <v>100</v>
+      </c>
+      <c r="F248">
+        <v>100000</v>
+      </c>
+      <c r="G248">
+        <v>50.80759768203426</v>
+      </c>
+      <c r="H248">
+        <v>27.432984</v>
+      </c>
+      <c r="I248">
+        <v>4.664526425000023E-07</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249">
+        <v>-1.3</v>
+      </c>
+      <c r="C249">
+        <v>4000</v>
+      </c>
+      <c r="D249">
+        <v>250</v>
+      </c>
+      <c r="E249">
+        <v>50</v>
+      </c>
+      <c r="F249">
+        <v>50000</v>
+      </c>
+      <c r="G249">
+        <v>49.4187461457364</v>
+      </c>
+      <c r="H249">
+        <v>16.63002</v>
+      </c>
+      <c r="I249">
+        <v>2.827820861014438E-07</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250">
+        <v>-1.4</v>
+      </c>
+      <c r="C250">
+        <v>4000</v>
+      </c>
+      <c r="D250">
+        <v>250</v>
+      </c>
+      <c r="E250">
+        <v>50</v>
+      </c>
+      <c r="F250">
+        <v>50000</v>
+      </c>
+      <c r="G250">
+        <v>49.41511753220595</v>
+      </c>
+      <c r="H250">
+        <v>16.964796</v>
+      </c>
+      <c r="I250">
+        <v>2.884747651283466E-07</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251">
+        <v>-1.5</v>
+      </c>
+      <c r="C251">
+        <v>4000</v>
+      </c>
+      <c r="D251">
+        <v>250</v>
+      </c>
+      <c r="E251">
+        <v>25</v>
+      </c>
+      <c r="F251">
+        <v>25000</v>
+      </c>
+      <c r="G251">
+        <v>49.57256593167755</v>
+      </c>
+      <c r="H251">
+        <v>10.505928</v>
+      </c>
+      <c r="I251">
+        <v>1.786449797905321E-07</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252">
+        <v>-0.9</v>
+      </c>
+      <c r="C252">
+        <v>5</v>
+      </c>
+      <c r="D252">
+        <v>1000</v>
+      </c>
+      <c r="E252">
+        <v>100</v>
+      </c>
+      <c r="F252">
+        <v>100000</v>
+      </c>
+      <c r="G252">
+        <v>42.26150003305286</v>
+      </c>
+      <c r="H252">
+        <v>0.06393600000000001</v>
+      </c>
+      <c r="I252">
+        <v>1.087505485236996E-09</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253">
+        <v>-1</v>
+      </c>
+      <c r="C253">
+        <v>5</v>
+      </c>
+      <c r="D253">
+        <v>1000</v>
+      </c>
+      <c r="E253">
+        <v>100</v>
+      </c>
+      <c r="F253">
+        <v>100000</v>
+      </c>
+      <c r="G253">
+        <v>46.37737032788888</v>
+      </c>
+      <c r="H253">
+        <v>0.031524</v>
+      </c>
+      <c r="I253">
+        <v>5.361105443277842E-10</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254">
+        <v>-1.1</v>
+      </c>
+      <c r="C254">
+        <v>5</v>
+      </c>
+      <c r="D254">
+        <v>1000</v>
+      </c>
+      <c r="E254">
+        <v>100</v>
+      </c>
+      <c r="F254">
+        <v>100000</v>
+      </c>
+      <c r="G254">
+        <v>48.8563584838824</v>
+      </c>
+      <c r="H254">
+        <v>0.042624</v>
+      </c>
+      <c r="I254">
+        <v>7.248085259427242E-10</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255">
+        <v>-1.2</v>
+      </c>
+      <c r="C255">
+        <v>5</v>
+      </c>
+      <c r="D255">
+        <v>1000</v>
+      </c>
+      <c r="E255">
+        <v>100</v>
+      </c>
+      <c r="F255">
+        <v>100000</v>
+      </c>
+      <c r="G255">
+        <v>58.34456053394913</v>
+      </c>
+      <c r="H255">
+        <v>0.268176</v>
+      </c>
+      <c r="I255">
+        <v>4.558488478161565E-09</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256">
+        <v>-1.3</v>
+      </c>
+      <c r="C256">
+        <v>5</v>
+      </c>
+      <c r="D256">
+        <v>1000</v>
+      </c>
+      <c r="E256">
+        <v>100</v>
+      </c>
+      <c r="F256">
+        <v>100000</v>
+      </c>
+      <c r="G256">
+        <v>48.48375456370228</v>
+      </c>
+      <c r="H256">
+        <v>0.266844</v>
+      </c>
+      <c r="I256">
+        <v>4.537672377828301E-09</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257">
+        <v>-1.4</v>
+      </c>
+      <c r="C257">
+        <v>5</v>
+      </c>
+      <c r="D257">
+        <v>1000</v>
+      </c>
+      <c r="E257">
+        <v>100</v>
+      </c>
+      <c r="F257">
+        <v>100000</v>
+      </c>
+      <c r="G257">
+        <v>44.79701903694631</v>
+      </c>
+      <c r="H257">
+        <v>0.08702400000000002</v>
+      </c>
+      <c r="I257">
+        <v>1.480062604491289E-09</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258">
+        <v>-1.5</v>
+      </c>
+      <c r="C258">
+        <v>5</v>
+      </c>
+      <c r="D258">
+        <v>1000</v>
+      </c>
+      <c r="E258">
+        <v>100</v>
+      </c>
+      <c r="F258">
+        <v>100000</v>
+      </c>
+      <c r="G258">
+        <v>40.22441784596152</v>
+      </c>
+      <c r="H258">
+        <v>0.05505600000000001</v>
+      </c>
+      <c r="I258">
+        <v>9.365409379171935E-10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" t="s">
+        <v>266</v>
+      </c>
+      <c r="B259">
+        <v>-0.9</v>
+      </c>
+      <c r="C259">
+        <v>10</v>
+      </c>
+      <c r="D259">
+        <v>1000</v>
+      </c>
+      <c r="E259">
+        <v>100</v>
+      </c>
+      <c r="F259">
+        <v>100000</v>
+      </c>
+      <c r="G259">
+        <v>44.06605580488689</v>
+      </c>
+      <c r="H259">
+        <v>0.05328000000000001</v>
+      </c>
+      <c r="I259">
+        <v>9.061878157291139E-10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" t="s">
+        <v>267</v>
+      </c>
+      <c r="B260">
+        <v>-1</v>
+      </c>
+      <c r="C260">
+        <v>10</v>
+      </c>
+      <c r="D260">
+        <v>1000</v>
+      </c>
+      <c r="E260">
+        <v>100</v>
+      </c>
+      <c r="F260">
+        <v>100000</v>
+      </c>
+      <c r="G260">
+        <v>42.5358786733555</v>
+      </c>
+      <c r="H260">
+        <v>0.05727600000000001</v>
+      </c>
+      <c r="I260">
+        <v>9.742127519338235E-10</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" t="s">
+        <v>268</v>
+      </c>
+      <c r="B261">
+        <v>-1.1</v>
+      </c>
+      <c r="C261">
+        <v>10</v>
+      </c>
+      <c r="D261">
+        <v>1000</v>
+      </c>
+      <c r="E261">
+        <v>100</v>
+      </c>
+      <c r="F261">
+        <v>100000</v>
+      </c>
+      <c r="G261">
+        <v>45.35338392346569</v>
+      </c>
+      <c r="H261">
+        <v>0.029304</v>
+      </c>
+      <c r="I261">
+        <v>4.983771100326471E-10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" t="s">
+        <v>269</v>
+      </c>
+      <c r="B262">
+        <v>-1.2</v>
+      </c>
+      <c r="C262">
+        <v>10</v>
+      </c>
+      <c r="D262">
+        <v>1000</v>
+      </c>
+      <c r="E262">
+        <v>100</v>
+      </c>
+      <c r="F262">
+        <v>100000</v>
+      </c>
+      <c r="G262">
+        <v>51.18008955861642</v>
+      </c>
+      <c r="H262">
+        <v>0.017316</v>
+      </c>
+      <c r="I262">
+        <v>2.944255419755331E-10</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" t="s">
+        <v>270</v>
+      </c>
+      <c r="B263">
+        <v>-1.3</v>
+      </c>
+      <c r="C263">
+        <v>10</v>
+      </c>
+      <c r="D263">
+        <v>1000</v>
+      </c>
+      <c r="E263">
+        <v>100</v>
+      </c>
+      <c r="F263">
+        <v>100000</v>
+      </c>
+      <c r="G263">
+        <v>47.17101866821643</v>
+      </c>
+      <c r="H263">
+        <v>0.02442</v>
+      </c>
+      <c r="I263">
+        <v>4.152834482212855E-10</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264">
+        <v>-1.4</v>
+      </c>
+      <c r="C264">
+        <v>10</v>
+      </c>
+      <c r="D264">
+        <v>1000</v>
+      </c>
+      <c r="E264">
+        <v>100</v>
+      </c>
+      <c r="F264">
+        <v>100000</v>
+      </c>
+      <c r="G264">
+        <v>53.30752759654927</v>
+      </c>
+      <c r="H264">
+        <v>0.039072</v>
+      </c>
+      <c r="I264">
+        <v>6.642871424020871E-10</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265">
+        <v>-1.5</v>
+      </c>
+      <c r="C265">
+        <v>10</v>
+      </c>
+      <c r="D265">
+        <v>1000</v>
+      </c>
+      <c r="E265">
+        <v>100</v>
+      </c>
+      <c r="F265">
+        <v>100000</v>
+      </c>
+      <c r="G265">
+        <v>48.6386006629043</v>
+      </c>
+      <c r="H265">
+        <v>0.352536</v>
+      </c>
+      <c r="I265">
+        <v>5.994823792517075E-09</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" t="s">
+        <v>273</v>
+      </c>
+      <c r="B266">
+        <v>-0.9</v>
+      </c>
+      <c r="C266">
+        <v>25</v>
+      </c>
+      <c r="D266">
+        <v>1000</v>
+      </c>
+      <c r="E266">
+        <v>100</v>
+      </c>
+      <c r="F266">
+        <v>100000</v>
+      </c>
+      <c r="G266">
+        <v>48.67853010579225</v>
+      </c>
+      <c r="H266">
+        <v>0.036408</v>
+      </c>
+      <c r="I266">
+        <v>6.191117757213848E-10</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" t="s">
+        <v>274</v>
+      </c>
+      <c r="B267">
+        <v>-1</v>
+      </c>
+      <c r="C267">
+        <v>25</v>
+      </c>
+      <c r="D267">
+        <v>1000</v>
+      </c>
+      <c r="E267">
+        <v>100</v>
+      </c>
+      <c r="F267">
+        <v>100000</v>
+      </c>
+      <c r="G267">
+        <v>46.35011796811844</v>
+      </c>
+      <c r="H267">
+        <v>0.13764</v>
+      </c>
+      <c r="I267">
+        <v>2.340766952147164E-09</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" t="s">
+        <v>275</v>
+      </c>
+      <c r="B268">
+        <v>-1.1</v>
+      </c>
+      <c r="C268">
+        <v>25</v>
+      </c>
+      <c r="D268">
+        <v>1000</v>
+      </c>
+      <c r="E268">
+        <v>100</v>
+      </c>
+      <c r="F268">
+        <v>100000</v>
+      </c>
+      <c r="G268">
+        <v>42.10827827215711</v>
+      </c>
+      <c r="H268">
+        <v>0.06837600000000001</v>
+      </c>
+      <c r="I268">
+        <v>1.163033974105778E-09</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" t="s">
+        <v>276</v>
+      </c>
+      <c r="B269">
+        <v>-1.2</v>
+      </c>
+      <c r="C269">
+        <v>25</v>
+      </c>
+      <c r="D269">
+        <v>1000</v>
+      </c>
+      <c r="E269">
+        <v>100</v>
+      </c>
+      <c r="F269">
+        <v>100000</v>
+      </c>
+      <c r="G269">
+        <v>41.24722149581589</v>
+      </c>
+      <c r="H269">
+        <v>0.04617600000000001</v>
+      </c>
+      <c r="I269">
+        <v>7.854531500403762E-10</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" t="s">
+        <v>277</v>
+      </c>
+      <c r="B270">
+        <v>-1.3</v>
+      </c>
+      <c r="C270">
+        <v>25</v>
+      </c>
+      <c r="D270">
+        <v>1000</v>
+      </c>
+      <c r="E270">
+        <v>100</v>
+      </c>
+      <c r="F270">
+        <v>100000</v>
+      </c>
+      <c r="G270">
+        <v>60.34194297336352</v>
+      </c>
+      <c r="H270">
+        <v>0.040404</v>
+      </c>
+      <c r="I270">
+        <v>6.867361801157966E-10</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" t="s">
+        <v>278</v>
+      </c>
+      <c r="B271">
+        <v>-1.4</v>
+      </c>
+      <c r="C271">
+        <v>25</v>
+      </c>
+      <c r="D271">
+        <v>1000</v>
+      </c>
+      <c r="E271">
+        <v>100</v>
+      </c>
+      <c r="F271">
+        <v>100000</v>
+      </c>
+      <c r="G271">
+        <v>50.87203717158511</v>
+      </c>
+      <c r="H271">
+        <v>0.136752</v>
+      </c>
+      <c r="I271">
+        <v>2.325236074451707E-09</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" t="s">
+        <v>279</v>
+      </c>
+      <c r="B272">
+        <v>-1.5</v>
+      </c>
+      <c r="C272">
+        <v>25</v>
+      </c>
+      <c r="D272">
+        <v>1000</v>
+      </c>
+      <c r="E272">
+        <v>100</v>
+      </c>
+      <c r="F272">
+        <v>100000</v>
+      </c>
+      <c r="G272">
+        <v>43.34035328373783</v>
+      </c>
+      <c r="H272">
+        <v>0.358752</v>
+      </c>
+      <c r="I272">
+        <v>6.101845378726323E-09</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" t="s">
+        <v>280</v>
+      </c>
+      <c r="B273">
+        <v>-0.9</v>
+      </c>
+      <c r="C273">
+        <v>2000</v>
+      </c>
+      <c r="D273">
+        <v>1000</v>
+      </c>
+      <c r="E273">
+        <v>100</v>
+      </c>
+      <c r="F273">
+        <v>100000</v>
+      </c>
+      <c r="G273">
+        <v>32.72259510205816</v>
+      </c>
+      <c r="H273">
+        <v>0.028416</v>
+      </c>
+      <c r="I273">
+        <v>4.835240554007708E-10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" t="s">
+        <v>281</v>
+      </c>
+      <c r="B274">
+        <v>-1</v>
+      </c>
+      <c r="C274">
+        <v>2000</v>
+      </c>
+      <c r="D274">
+        <v>1000</v>
+      </c>
+      <c r="E274">
+        <v>100</v>
+      </c>
+      <c r="F274">
+        <v>100000</v>
+      </c>
+      <c r="G274">
+        <v>82.16095603174276</v>
+      </c>
+      <c r="H274">
+        <v>5.154396</v>
+      </c>
+      <c r="I274">
+        <v>8.753000991123091E-08</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275">
+        <v>-1.1</v>
+      </c>
+      <c r="C275">
+        <v>2000</v>
+      </c>
+      <c r="D275">
+        <v>1000</v>
+      </c>
+      <c r="E275">
+        <v>100</v>
+      </c>
+      <c r="F275">
+        <v>100000</v>
+      </c>
+      <c r="G275">
+        <v>65.36166552543816</v>
+      </c>
+      <c r="H275">
+        <v>19.270932</v>
+      </c>
+      <c r="I275">
+        <v>3.274759159807272E-07</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" t="s">
+        <v>283</v>
+      </c>
+      <c r="B276">
+        <v>-1.2</v>
+      </c>
+      <c r="C276">
+        <v>2000</v>
+      </c>
+      <c r="D276">
+        <v>1000</v>
+      </c>
+      <c r="E276">
+        <v>50</v>
+      </c>
+      <c r="F276">
+        <v>50000</v>
+      </c>
+      <c r="G276">
+        <v>55.40011777408696</v>
+      </c>
+      <c r="H276">
+        <v>15.53334</v>
+      </c>
+      <c r="I276">
+        <v>2.640693349222607E-07</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" t="s">
+        <v>284</v>
+      </c>
+      <c r="B277">
+        <v>-1.3</v>
+      </c>
+      <c r="C277">
+        <v>2000</v>
+      </c>
+      <c r="D277">
+        <v>1000</v>
+      </c>
+      <c r="E277">
+        <v>25</v>
+      </c>
+      <c r="F277">
+        <v>25000</v>
+      </c>
+      <c r="G277">
+        <v>51.04959895279598</v>
+      </c>
+      <c r="H277">
+        <v>10.217328</v>
+      </c>
+      <c r="I277">
+        <v>1.737270936054881E-07</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" t="s">
+        <v>285</v>
+      </c>
+      <c r="B278">
+        <v>-1.4</v>
+      </c>
+      <c r="C278">
+        <v>2000</v>
+      </c>
+      <c r="D278">
+        <v>1000</v>
+      </c>
+      <c r="E278">
+        <v>25</v>
+      </c>
+      <c r="F278">
+        <v>25000</v>
+      </c>
+      <c r="G278">
+        <v>49.82789994198192</v>
+      </c>
+      <c r="H278">
+        <v>11.404584</v>
+      </c>
+      <c r="I278">
+        <v>1.939238921671727E-07</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279" t="s">
+        <v>286</v>
+      </c>
+      <c r="B279">
+        <v>-1.5</v>
+      </c>
+      <c r="C279">
+        <v>2000</v>
+      </c>
+      <c r="D279">
+        <v>1000</v>
+      </c>
+      <c r="E279">
+        <v>10</v>
+      </c>
+      <c r="F279">
+        <v>10000</v>
+      </c>
+      <c r="G279">
+        <v>50.21519986429573</v>
+      </c>
+      <c r="H279">
+        <v>5.87856</v>
+      </c>
+      <c r="I279">
+        <v>9.995763261204667E-08</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280" t="s">
+        <v>287</v>
+      </c>
+      <c r="B280">
+        <v>-0.9</v>
+      </c>
+      <c r="C280">
+        <v>4000</v>
+      </c>
+      <c r="D280">
+        <v>1000</v>
+      </c>
+      <c r="E280">
+        <v>100</v>
+      </c>
+      <c r="F280">
+        <v>100000</v>
+      </c>
+      <c r="G280">
+        <v>78.9684471943695</v>
+      </c>
+      <c r="H280">
+        <v>0.18426</v>
+      </c>
+      <c r="I280">
+        <v>3.129441045495352E-09</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281" t="s">
+        <v>288</v>
+      </c>
+      <c r="B281">
+        <v>-1</v>
+      </c>
+      <c r="C281">
+        <v>4000</v>
+      </c>
+      <c r="D281">
+        <v>1000</v>
+      </c>
+      <c r="E281">
+        <v>100</v>
+      </c>
+      <c r="F281">
+        <v>100000</v>
+      </c>
+      <c r="G281">
+        <v>73.36907904045832</v>
+      </c>
+      <c r="H281">
+        <v>9.566868000000001</v>
+      </c>
+      <c r="I281">
+        <v>1.625191801299352E-07</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282">
+        <v>-1.1</v>
+      </c>
+      <c r="C282">
+        <v>4000</v>
+      </c>
+      <c r="D282">
+        <v>1000</v>
+      </c>
+      <c r="E282">
+        <v>100</v>
+      </c>
+      <c r="F282">
+        <v>100000</v>
+      </c>
+      <c r="G282">
+        <v>57.66065275224649</v>
+      </c>
+      <c r="H282">
+        <v>19.026732</v>
+      </c>
+      <c r="I282">
+        <v>3.23427743541559E-07</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283" t="s">
+        <v>290</v>
+      </c>
+      <c r="B283">
+        <v>-1.2</v>
+      </c>
+      <c r="C283">
+        <v>4000</v>
+      </c>
+      <c r="D283">
+        <v>1000</v>
+      </c>
+      <c r="E283">
+        <v>50</v>
+      </c>
+      <c r="F283">
+        <v>50000</v>
+      </c>
+      <c r="G283">
+        <v>51.16577352949402</v>
+      </c>
+      <c r="H283">
+        <v>15.270048</v>
+      </c>
+      <c r="I283">
+        <v>2.596381834658787E-07</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" t="s">
+        <v>291</v>
+      </c>
+      <c r="B284">
+        <v>-1.3</v>
+      </c>
+      <c r="C284">
+        <v>4000</v>
+      </c>
+      <c r="D284">
+        <v>1000</v>
+      </c>
+      <c r="E284">
+        <v>25</v>
+      </c>
+      <c r="F284">
+        <v>25000</v>
+      </c>
+      <c r="G284">
+        <v>50.39298639555047</v>
+      </c>
+      <c r="H284">
+        <v>9.238752000000002</v>
+      </c>
+      <c r="I284">
+        <v>1.570923964560591E-07</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285" t="s">
+        <v>292</v>
+      </c>
+      <c r="B285">
+        <v>-1.4</v>
+      </c>
+      <c r="C285">
+        <v>4000</v>
+      </c>
+      <c r="D285">
+        <v>1000</v>
+      </c>
+      <c r="E285">
+        <v>25</v>
+      </c>
+      <c r="F285">
+        <v>25000</v>
+      </c>
+      <c r="G285">
+        <v>49.48900655831547</v>
+      </c>
+      <c r="H285">
+        <v>9.336432</v>
+      </c>
+      <c r="I285">
+        <v>1.587591685044277E-07</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286" t="s">
+        <v>293</v>
+      </c>
+      <c r="B286">
+        <v>-1.5</v>
+      </c>
+      <c r="C286">
+        <v>4000</v>
+      </c>
+      <c r="D286">
+        <v>1000</v>
+      </c>
+      <c r="E286">
+        <v>10</v>
+      </c>
+      <c r="F286">
+        <v>10000</v>
+      </c>
+      <c r="G286">
+        <v>49.7714646870897</v>
+      </c>
+      <c r="H286">
+        <v>6.492612</v>
+      </c>
+      <c r="I286">
+        <v>1.104008255937652E-07</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>